--- a/research/traditional_assets/database/data/brazil/brazil_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_retail_grocery_and_food.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08734520694238009</v>
+        <v>0.087077933238776</v>
       </c>
       <c r="C2">
-        <v>1694.539942318571</v>
+        <v>1684.169970228726</v>
       </c>
       <c r="D2">
-        <v>1274.139942318571</v>
+        <v>1282.389970228725</v>
       </c>
       <c r="E2">
-        <v>-1660</v>
+        <v>-1641.38</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18.62</v>
       </c>
       <c r="G2">
         <v>420.4</v>
@@ -1445,28 +1445,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.936586</v>
       </c>
       <c r="N2">
-        <v>49.09999999999999</v>
+        <v>48.163414</v>
       </c>
       <c r="O2">
-        <v>16.694</v>
+        <v>16.37556076</v>
       </c>
       <c r="P2">
-        <v>32.40599999999999</v>
+        <v>31.78785324</v>
       </c>
       <c r="Q2">
-        <v>224.306</v>
+        <v>223.68785324</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08734520694238009</v>
+        <v>0.08762217498866262</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5450831406406319</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>52.42444367094959</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.087077933238776</v>
+        <v>0.08681065953517191</v>
       </c>
       <c r="C3">
-        <v>1684.169970228726</v>
+        <v>1673.907531913726</v>
       </c>
       <c r="D3">
-        <v>1282.389970228725</v>
+        <v>1290.747531913726</v>
       </c>
       <c r="E3">
-        <v>-1641.38</v>
+        <v>-1622.76</v>
       </c>
       <c r="F3">
-        <v>18.62</v>
+        <v>37.24</v>
       </c>
       <c r="G3">
         <v>420.4</v>
@@ -1527,28 +1527,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M3">
-        <v>0.936586</v>
+        <v>1.873172</v>
       </c>
       <c r="N3">
-        <v>48.163414</v>
+        <v>47.226828</v>
       </c>
       <c r="O3">
-        <v>16.37556076</v>
+        <v>16.05712152</v>
       </c>
       <c r="P3">
-        <v>31.78785324</v>
+        <v>31.16970648</v>
       </c>
       <c r="Q3">
-        <v>223.68785324</v>
+        <v>223.06970648</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08762217498866262</v>
+        <v>0.08790479544405295</v>
       </c>
       <c r="T3">
-        <v>0.5450831406406319</v>
+        <v>0.5487666326033338</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>52.42444367094959</v>
+        <v>26.2122218354748</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08681065953517191</v>
+        <v>0.08654338583156782</v>
       </c>
       <c r="C4">
-        <v>1673.907531913726</v>
+        <v>1663.754743615242</v>
       </c>
       <c r="D4">
-        <v>1290.747531913726</v>
+        <v>1299.214743615242</v>
       </c>
       <c r="E4">
-        <v>-1622.76</v>
+        <v>-1604.14</v>
       </c>
       <c r="F4">
-        <v>37.24</v>
+        <v>55.86</v>
       </c>
       <c r="G4">
         <v>420.4</v>
@@ -1609,28 +1609,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M4">
-        <v>1.873172</v>
+        <v>2.809758</v>
       </c>
       <c r="N4">
-        <v>47.226828</v>
+        <v>46.29024199999999</v>
       </c>
       <c r="O4">
-        <v>16.05712152</v>
+        <v>15.73868228</v>
       </c>
       <c r="P4">
-        <v>31.16970648</v>
+        <v>30.55155971999999</v>
       </c>
       <c r="Q4">
-        <v>223.06970648</v>
+        <v>222.45155972</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08790479544405295</v>
+        <v>0.08819324312532764</v>
       </c>
       <c r="T4">
-        <v>0.5487666326033338</v>
+        <v>0.5525260728539266</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>26.2122218354748</v>
+        <v>17.4748145569832</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08654338583156782</v>
+        <v>0.08627611212796371</v>
       </c>
       <c r="C5">
-        <v>1663.754743615242</v>
+        <v>1653.713777471194</v>
       </c>
       <c r="D5">
-        <v>1299.214743615242</v>
+        <v>1307.793777471194</v>
       </c>
       <c r="E5">
-        <v>-1604.14</v>
+        <v>-1585.52</v>
       </c>
       <c r="F5">
-        <v>55.86</v>
+        <v>74.48</v>
       </c>
       <c r="G5">
         <v>420.4</v>
@@ -1691,28 +1691,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M5">
-        <v>2.809758</v>
+        <v>3.746344</v>
       </c>
       <c r="N5">
-        <v>46.29024199999999</v>
+        <v>45.35365599999999</v>
       </c>
       <c r="O5">
-        <v>15.73868228</v>
+        <v>15.42024304</v>
       </c>
       <c r="P5">
-        <v>30.55155971999999</v>
+        <v>29.93341295999999</v>
       </c>
       <c r="Q5">
-        <v>222.45155972</v>
+        <v>221.83341296</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08819324312532764</v>
+        <v>0.08848770013329554</v>
       </c>
       <c r="T5">
-        <v>0.5525260728539266</v>
+        <v>0.5563638347764066</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>17.4748145569832</v>
+        <v>13.1061109177374</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08627611212796371</v>
+        <v>0.08605833842435962</v>
       </c>
       <c r="C6">
-        <v>1653.713777471194</v>
+        <v>1642.16816517861</v>
       </c>
       <c r="D6">
-        <v>1307.793777471194</v>
+        <v>1314.86816517861</v>
       </c>
       <c r="E6">
-        <v>-1585.52</v>
+        <v>-1566.9</v>
       </c>
       <c r="F6">
-        <v>74.48</v>
+        <v>93.10000000000001</v>
       </c>
       <c r="G6">
         <v>420.4</v>
@@ -1773,45 +1773,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M6">
-        <v>3.746344</v>
+        <v>4.82258</v>
       </c>
       <c r="N6">
-        <v>45.35365599999999</v>
+        <v>44.27741999999999</v>
       </c>
       <c r="O6">
-        <v>15.42024304</v>
+        <v>15.0543228</v>
       </c>
       <c r="P6">
-        <v>29.93341295999999</v>
+        <v>29.22309719999999</v>
       </c>
       <c r="Q6">
-        <v>221.83341296</v>
+        <v>221.1230972</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08848770013329554</v>
+        <v>0.08878835623616801</v>
       </c>
       <c r="T6">
-        <v>0.5563638347764066</v>
+        <v>0.5602823916867283</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.34</v>
       </c>
       <c r="W6">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.1061109177374</v>
+        <v>10.18127226505314</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08605833842435962</v>
+        <v>0.08586828472075553</v>
       </c>
       <c r="C7">
-        <v>1642.16816517861</v>
+        <v>1629.784907437104</v>
       </c>
       <c r="D7">
-        <v>1314.86816517861</v>
+        <v>1321.104907437104</v>
       </c>
       <c r="E7">
-        <v>-1566.9</v>
+        <v>-1548.28</v>
       </c>
       <c r="F7">
-        <v>93.10000000000001</v>
+        <v>111.72</v>
       </c>
       <c r="G7">
         <v>420.4</v>
@@ -1855,45 +1855,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M7">
-        <v>4.82258</v>
+        <v>5.97702</v>
       </c>
       <c r="N7">
-        <v>44.27741999999999</v>
+        <v>43.12297999999999</v>
       </c>
       <c r="O7">
-        <v>15.0543228</v>
+        <v>14.6618132</v>
       </c>
       <c r="P7">
-        <v>29.22309719999999</v>
+        <v>28.46116679999999</v>
       </c>
       <c r="Q7">
-        <v>221.1230972</v>
+        <v>220.3611668</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08878835623616801</v>
+        <v>0.08909540927739951</v>
       </c>
       <c r="T7">
-        <v>0.5602823916867283</v>
+        <v>0.5642843221483336</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.34</v>
       </c>
       <c r="W7">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.18127226505314</v>
+        <v>8.214796002021071</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08586828472075553</v>
+        <v>0.08565909101715143</v>
       </c>
       <c r="C8">
-        <v>1629.784907437104</v>
+        <v>1618.098503296513</v>
       </c>
       <c r="D8">
-        <v>1321.104907437104</v>
+        <v>1328.038503296513</v>
       </c>
       <c r="E8">
-        <v>-1548.28</v>
+        <v>-1529.66</v>
       </c>
       <c r="F8">
-        <v>111.72</v>
+        <v>130.34</v>
       </c>
       <c r="G8">
         <v>420.4</v>
@@ -1937,45 +1937,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M8">
-        <v>5.97702</v>
+        <v>7.077461999999999</v>
       </c>
       <c r="N8">
-        <v>43.12298</v>
+        <v>42.022538</v>
       </c>
       <c r="O8">
-        <v>14.6618132</v>
+        <v>14.28766292</v>
       </c>
       <c r="P8">
-        <v>28.4611668</v>
+        <v>27.73487507999999</v>
       </c>
       <c r="Q8">
-        <v>220.3611668</v>
+        <v>219.63487508</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08909540927739951</v>
+        <v>0.08940906560984024</v>
       </c>
       <c r="T8">
-        <v>0.5642843221483336</v>
+        <v>0.5683723156306183</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.34</v>
       </c>
       <c r="W8">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.214796002021075</v>
+        <v>6.937515171399014</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08565909101715143</v>
+        <v>0.08547101731354734</v>
       </c>
       <c r="C9">
-        <v>1618.098503296513</v>
+        <v>1605.774513249313</v>
       </c>
       <c r="D9">
-        <v>1328.038503296513</v>
+        <v>1334.334513249313</v>
       </c>
       <c r="E9">
-        <v>-1529.66</v>
+        <v>-1511.04</v>
       </c>
       <c r="F9">
-        <v>130.34</v>
+        <v>148.96</v>
       </c>
       <c r="G9">
         <v>420.4</v>
@@ -2019,45 +2019,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M9">
-        <v>7.077462000000001</v>
+        <v>8.237488000000001</v>
       </c>
       <c r="N9">
-        <v>42.022538</v>
+        <v>40.862512</v>
       </c>
       <c r="O9">
-        <v>14.28766292</v>
+        <v>13.89325408</v>
       </c>
       <c r="P9">
-        <v>27.73487507999999</v>
+        <v>26.96925792</v>
       </c>
       <c r="Q9">
-        <v>219.63487508</v>
+        <v>218.86925792</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08940906560984026</v>
+        <v>0.08972954055820363</v>
       </c>
       <c r="T9">
-        <v>0.5683723156306184</v>
+        <v>0.5725491785364311</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.34</v>
       </c>
       <c r="W9">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.937515171399012</v>
+        <v>5.9605549653001</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08547101731354734</v>
+        <v>0.08523674360994325</v>
       </c>
       <c r="C10">
-        <v>1605.774513249313</v>
+        <v>1595.081118228606</v>
       </c>
       <c r="D10">
-        <v>1334.334513249313</v>
+        <v>1342.261118228606</v>
       </c>
       <c r="E10">
-        <v>-1511.04</v>
+        <v>-1492.42</v>
       </c>
       <c r="F10">
-        <v>148.96</v>
+        <v>167.58</v>
       </c>
       <c r="G10">
         <v>420.4</v>
@@ -2101,28 +2101,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M10">
-        <v>8.237488000000001</v>
+        <v>9.267173999999999</v>
       </c>
       <c r="N10">
-        <v>40.862512</v>
+        <v>39.832826</v>
       </c>
       <c r="O10">
-        <v>13.89325408</v>
+        <v>13.54316084</v>
       </c>
       <c r="P10">
-        <v>26.96925792</v>
+        <v>26.28966516</v>
       </c>
       <c r="Q10">
-        <v>218.86925792</v>
+        <v>218.18966516</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08972954055820363</v>
+        <v>0.09005705891202556</v>
       </c>
       <c r="T10">
-        <v>0.5725491785364311</v>
+        <v>0.576817840626987</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.9605549653001</v>
+        <v>5.298271080266757</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08523674360994325</v>
+        <v>0.08500246990633915</v>
       </c>
       <c r="C11">
-        <v>1595.081118228606</v>
+        <v>1584.482461886862</v>
       </c>
       <c r="D11">
-        <v>1342.261118228606</v>
+        <v>1350.282461886862</v>
       </c>
       <c r="E11">
-        <v>-1492.42</v>
+        <v>-1473.8</v>
       </c>
       <c r="F11">
-        <v>167.58</v>
+        <v>186.2</v>
       </c>
       <c r="G11">
         <v>420.4</v>
@@ -2183,28 +2183,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M11">
-        <v>9.267173999999999</v>
+        <v>10.29686</v>
       </c>
       <c r="N11">
-        <v>39.832826</v>
+        <v>38.80313999999999</v>
       </c>
       <c r="O11">
-        <v>13.54316084</v>
+        <v>13.1930676</v>
       </c>
       <c r="P11">
-        <v>26.28966516</v>
+        <v>25.61007239999999</v>
       </c>
       <c r="Q11">
-        <v>218.18966516</v>
+        <v>217.5100724</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09005705891202556</v>
+        <v>0.09039185545148795</v>
       </c>
       <c r="T11">
-        <v>0.576817840626987</v>
+        <v>0.5811813618751108</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.298271080266757</v>
+        <v>4.76844397224008</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08500246990633915</v>
+        <v>0.08494969620273507</v>
       </c>
       <c r="C12">
-        <v>1584.482461886862</v>
+        <v>1567.68263964907</v>
       </c>
       <c r="D12">
-        <v>1350.282461886862</v>
+        <v>1352.10263964907</v>
       </c>
       <c r="E12">
-        <v>-1473.8</v>
+        <v>-1455.18</v>
       </c>
       <c r="F12">
-        <v>186.2</v>
+        <v>204.82</v>
       </c>
       <c r="G12">
         <v>420.4</v>
@@ -2265,45 +2265,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M12">
-        <v>10.29686</v>
+        <v>11.838596</v>
       </c>
       <c r="N12">
-        <v>38.80313999999999</v>
+        <v>37.26140399999999</v>
       </c>
       <c r="O12">
-        <v>13.1930676</v>
+        <v>12.66887736</v>
       </c>
       <c r="P12">
-        <v>25.61007239999999</v>
+        <v>24.59252664</v>
       </c>
       <c r="Q12">
-        <v>217.5100724</v>
+        <v>216.49252664</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09039185545148795</v>
+        <v>0.09073417550869109</v>
       </c>
       <c r="T12">
-        <v>0.5811813618751108</v>
+        <v>0.5856429397804959</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.34</v>
       </c>
       <c r="W12">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.76844397224008</v>
+        <v>4.147451268714634</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08494969620273507</v>
+        <v>0.08500912249913098</v>
       </c>
       <c r="C13">
-        <v>1567.68263964907</v>
+        <v>1547.013360116654</v>
       </c>
       <c r="D13">
-        <v>1352.10263964907</v>
+        <v>1350.053360116653</v>
       </c>
       <c r="E13">
-        <v>-1455.18</v>
+        <v>-1436.56</v>
       </c>
       <c r="F13">
-        <v>204.82</v>
+        <v>223.44</v>
       </c>
       <c r="G13">
         <v>420.4</v>
@@ -2347,45 +2347,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M13">
-        <v>11.838596</v>
+        <v>13.696872</v>
       </c>
       <c r="N13">
-        <v>37.26140399999999</v>
+        <v>35.403128</v>
       </c>
       <c r="O13">
-        <v>12.66887736</v>
+        <v>12.03706352</v>
       </c>
       <c r="P13">
-        <v>24.59252664</v>
+        <v>23.36606448</v>
       </c>
       <c r="Q13">
-        <v>216.49252664</v>
+        <v>215.26606448</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09073417550869109</v>
+        <v>0.09108427556719428</v>
       </c>
       <c r="T13">
-        <v>0.5856429397804959</v>
+        <v>0.5902059171837306</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.34</v>
       </c>
       <c r="W13">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.147451268714634</v>
+        <v>3.584760082448021</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08500912249913098</v>
+        <v>0.08505468879552688</v>
       </c>
       <c r="C14">
-        <v>1547.013360116654</v>
+        <v>1526.826236966658</v>
       </c>
       <c r="D14">
-        <v>1350.053360116653</v>
+        <v>1348.486236966658</v>
       </c>
       <c r="E14">
-        <v>-1436.56</v>
+        <v>-1417.94</v>
       </c>
       <c r="F14">
-        <v>223.44</v>
+        <v>242.06</v>
       </c>
       <c r="G14">
         <v>420.4</v>
@@ -2429,45 +2429,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M14">
-        <v>13.696872</v>
+        <v>15.516046</v>
       </c>
       <c r="N14">
-        <v>35.403128</v>
+        <v>33.58395399999999</v>
       </c>
       <c r="O14">
-        <v>12.03706352</v>
+        <v>11.41854436</v>
       </c>
       <c r="P14">
-        <v>23.36606448</v>
+        <v>22.16540963999999</v>
       </c>
       <c r="Q14">
-        <v>215.26606448</v>
+        <v>214.06540964</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09108427556719428</v>
+        <v>0.09144242390290447</v>
       </c>
       <c r="T14">
-        <v>0.5902059171837306</v>
+        <v>0.5948737906192236</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.34</v>
       </c>
       <c r="W14">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.584760082448021</v>
+        <v>3.164465998618462</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08505468879552688</v>
+        <v>0.08559921509192278</v>
       </c>
       <c r="C15">
-        <v>1526.826236966658</v>
+        <v>1489.756470692113</v>
       </c>
       <c r="D15">
-        <v>1348.486236966658</v>
+        <v>1330.036470692113</v>
       </c>
       <c r="E15">
-        <v>-1417.94</v>
+        <v>-1399.32</v>
       </c>
       <c r="F15">
-        <v>242.06</v>
+        <v>260.68</v>
       </c>
       <c r="G15">
         <v>420.4</v>
@@ -2511,45 +2511,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M15">
-        <v>15.516046</v>
+        <v>18.742892</v>
       </c>
       <c r="N15">
-        <v>33.58395399999999</v>
+        <v>30.35710799999999</v>
       </c>
       <c r="O15">
-        <v>11.41854436</v>
+        <v>10.32141672</v>
       </c>
       <c r="P15">
-        <v>22.16540963999999</v>
+        <v>20.03569127999999</v>
       </c>
       <c r="Q15">
-        <v>214.06540964</v>
+        <v>211.93569128</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09144242390290447</v>
+        <v>0.09180890126967767</v>
       </c>
       <c r="T15">
-        <v>0.5948737906192236</v>
+        <v>0.5996502192508908</v>
       </c>
       <c r="U15">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V15">
         <v>0.34</v>
       </c>
       <c r="W15">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.164465998618462</v>
+        <v>2.619659762218125</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08559921509192278</v>
+        <v>0.08586060138831869</v>
       </c>
       <c r="C16">
-        <v>1489.756470692113</v>
+        <v>1462.458285764837</v>
       </c>
       <c r="D16">
-        <v>1330.036470692113</v>
+        <v>1321.358285764838</v>
       </c>
       <c r="E16">
-        <v>-1399.32</v>
+        <v>-1380.7</v>
       </c>
       <c r="F16">
-        <v>260.68</v>
+        <v>279.3000000000001</v>
       </c>
       <c r="G16">
         <v>420.4</v>
@@ -2593,45 +2593,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M16">
-        <v>18.742892</v>
+        <v>21.17094000000001</v>
       </c>
       <c r="N16">
-        <v>30.35710799999999</v>
+        <v>27.92905999999999</v>
       </c>
       <c r="O16">
-        <v>10.32141672</v>
+        <v>9.495880399999997</v>
       </c>
       <c r="P16">
-        <v>20.03569127999999</v>
+        <v>18.43317959999999</v>
       </c>
       <c r="Q16">
-        <v>211.93569128</v>
+        <v>210.3331796</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09180890126967767</v>
+        <v>0.09218400163331611</v>
       </c>
       <c r="T16">
-        <v>0.5996502192508908</v>
+        <v>0.6045390344385972</v>
       </c>
       <c r="U16">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.34</v>
       </c>
       <c r="W16">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.619659762218125</v>
+        <v>2.3192168132355</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08586060138831869</v>
+        <v>0.0857616276847146</v>
       </c>
       <c r="C17">
-        <v>1462.458285764838</v>
+        <v>1447.110918310286</v>
       </c>
       <c r="D17">
-        <v>1321.358285764838</v>
+        <v>1324.630918310286</v>
       </c>
       <c r="E17">
-        <v>-1380.7</v>
+        <v>-1362.08</v>
       </c>
       <c r="F17">
-        <v>279.3</v>
+        <v>297.92</v>
       </c>
       <c r="G17">
         <v>420.4</v>
@@ -2675,28 +2675,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M17">
-        <v>21.17094</v>
+        <v>22.582336</v>
       </c>
       <c r="N17">
-        <v>27.92905999999999</v>
+        <v>26.51766399999999</v>
       </c>
       <c r="O17">
-        <v>9.495880399999999</v>
+        <v>9.016005759999999</v>
       </c>
       <c r="P17">
-        <v>18.4331796</v>
+        <v>17.50165823999999</v>
       </c>
       <c r="Q17">
-        <v>210.3331796</v>
+        <v>209.40165824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09218400163331611</v>
+        <v>0.09256803295799358</v>
       </c>
       <c r="T17">
-        <v>0.6045390344385972</v>
+        <v>0.6095442499879158</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.319216813235501</v>
+        <v>2.174265762408282</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0857616276847146</v>
+        <v>0.08566265398111052</v>
       </c>
       <c r="C18">
-        <v>1447.110918310286</v>
+        <v>1431.779801884265</v>
       </c>
       <c r="D18">
-        <v>1324.630918310286</v>
+        <v>1327.919801884264</v>
       </c>
       <c r="E18">
-        <v>-1362.08</v>
+        <v>-1343.46</v>
       </c>
       <c r="F18">
-        <v>297.92</v>
+        <v>316.54</v>
       </c>
       <c r="G18">
         <v>420.4</v>
@@ -2757,28 +2757,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M18">
-        <v>22.582336</v>
+        <v>23.993732</v>
       </c>
       <c r="N18">
-        <v>26.51766399999999</v>
+        <v>25.10626799999999</v>
       </c>
       <c r="O18">
-        <v>9.016005759999999</v>
+        <v>8.536131119999997</v>
       </c>
       <c r="P18">
-        <v>17.50165823999999</v>
+        <v>16.57013687999999</v>
       </c>
       <c r="Q18">
-        <v>209.40165824</v>
+        <v>208.47013688</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09256803295799358</v>
+        <v>0.09296131804953074</v>
       </c>
       <c r="T18">
-        <v>0.6095442499879158</v>
+        <v>0.6146700731408323</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.174265762408282</v>
+        <v>2.046367776384265</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08566265398111052</v>
+        <v>0.08725064027750641</v>
       </c>
       <c r="C19">
-        <v>1431.779801884265</v>
+        <v>1362.286801274686</v>
       </c>
       <c r="D19">
-        <v>1327.919801884264</v>
+        <v>1277.046801274687</v>
       </c>
       <c r="E19">
-        <v>-1343.46</v>
+        <v>-1324.84</v>
       </c>
       <c r="F19">
-        <v>316.54</v>
+        <v>335.16</v>
       </c>
       <c r="G19">
         <v>420.4</v>
@@ -2839,45 +2839,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M19">
-        <v>23.993732</v>
+        <v>30.1644</v>
       </c>
       <c r="N19">
-        <v>25.10626799999999</v>
+        <v>18.93559999999999</v>
       </c>
       <c r="O19">
-        <v>8.536131119999997</v>
+        <v>6.438103999999998</v>
       </c>
       <c r="P19">
-        <v>16.57013687999999</v>
+        <v>12.49749599999999</v>
       </c>
       <c r="Q19">
-        <v>208.47013688</v>
+        <v>204.397496</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09296131804953074</v>
+        <v>0.09336419546037368</v>
       </c>
       <c r="T19">
-        <v>0.6146700731408323</v>
+        <v>0.6199209163706492</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.34</v>
       </c>
       <c r="W19">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.046367776384265</v>
+        <v>1.627746615215287</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08725064027750641</v>
+        <v>0.08724538657390235</v>
       </c>
       <c r="C20">
-        <v>1362.286801274687</v>
+        <v>1343.828682389499</v>
       </c>
       <c r="D20">
-        <v>1277.046801274687</v>
+        <v>1277.208682389499</v>
       </c>
       <c r="E20">
-        <v>-1324.84</v>
+        <v>-1306.22</v>
       </c>
       <c r="F20">
-        <v>335.16</v>
+        <v>353.78</v>
       </c>
       <c r="G20">
         <v>420.4</v>
@@ -2921,28 +2921,28 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M20">
-        <v>30.1644</v>
+        <v>31.8402</v>
       </c>
       <c r="N20">
-        <v>18.9356</v>
+        <v>17.25979999999999</v>
       </c>
       <c r="O20">
-        <v>6.438103999999999</v>
+        <v>5.868331999999998</v>
       </c>
       <c r="P20">
-        <v>12.497496</v>
+        <v>11.39146799999999</v>
       </c>
       <c r="Q20">
-        <v>204.397496</v>
+        <v>203.291468</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09336419546037368</v>
+        <v>0.09377702046160782</v>
       </c>
       <c r="T20">
-        <v>0.6199209163706492</v>
+        <v>0.6253014100505851</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.627746615215287</v>
+        <v>1.542075740730271</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08724538657390235</v>
+        <v>0.09604225647784748</v>
       </c>
       <c r="C21">
-        <v>1343.828682389499</v>
+        <v>1101.583403454755</v>
       </c>
       <c r="D21">
-        <v>1277.208682389499</v>
+        <v>1053.583403454755</v>
       </c>
       <c r="E21">
-        <v>-1306.22</v>
+        <v>-1287.6</v>
       </c>
       <c r="F21">
-        <v>353.78</v>
+        <v>372.4</v>
       </c>
       <c r="G21">
         <v>420.4</v>
@@ -3003,45 +3003,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M21">
-        <v>31.8402</v>
+        <v>54.66832000000001</v>
       </c>
       <c r="N21">
-        <v>17.25979999999999</v>
+        <v>-5.568320000000014</v>
       </c>
       <c r="O21">
-        <v>5.868331999999998</v>
+        <v>-1.893228800000005</v>
       </c>
       <c r="P21">
-        <v>11.39146799999999</v>
+        <v>-3.675091200000009</v>
       </c>
       <c r="Q21">
-        <v>203.291468</v>
+        <v>188.2249088</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09377702046160782</v>
+        <v>0.09455985604306658</v>
       </c>
       <c r="T21">
-        <v>0.6253014100505851</v>
+        <v>0.6355043819778569</v>
       </c>
       <c r="U21">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.34</v>
+        <v>0.3053688132358923</v>
       </c>
       <c r="W21">
-        <v>0.05939999999999999</v>
+        <v>0.101971858216971</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.542075740730271</v>
+        <v>0.8981435683408597</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09604225647784748</v>
+        <v>0.09705225647784746</v>
       </c>
       <c r="C22">
-        <v>1101.583403454755</v>
+        <v>1062.201015403622</v>
       </c>
       <c r="D22">
-        <v>1053.583403454755</v>
+        <v>1032.821015403622</v>
       </c>
       <c r="E22">
-        <v>-1287.6</v>
+        <v>-1268.98</v>
       </c>
       <c r="F22">
-        <v>372.4</v>
+        <v>391.02</v>
       </c>
       <c r="G22">
         <v>420.4</v>
@@ -3085,37 +3085,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M22">
-        <v>54.66832000000001</v>
+        <v>57.40173600000001</v>
       </c>
       <c r="N22">
-        <v>-5.568320000000014</v>
+        <v>-8.30173600000002</v>
       </c>
       <c r="O22">
-        <v>-1.893228800000005</v>
+        <v>-2.822590240000007</v>
       </c>
       <c r="P22">
-        <v>-3.675091200000009</v>
+        <v>-5.479145760000012</v>
       </c>
       <c r="Q22">
-        <v>188.2249088</v>
+        <v>186.42085424</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09455985604306658</v>
+        <v>0.09517706941070031</v>
       </c>
       <c r="T22">
-        <v>0.6355043819778569</v>
+        <v>0.6435487412433993</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.3053688132358923</v>
+        <v>0.2908274411770403</v>
       </c>
       <c r="W22">
-        <v>0.101971858216971</v>
+        <v>0.1041065316352105</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8981435683408597</v>
+        <v>0.8553748269912949</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09705225647784746</v>
+        <v>0.09806225647784746</v>
       </c>
       <c r="C23">
-        <v>1062.201015403622</v>
+        <v>1023.621118991575</v>
       </c>
       <c r="D23">
-        <v>1032.821015403622</v>
+        <v>1012.861118991575</v>
       </c>
       <c r="E23">
-        <v>-1268.98</v>
+        <v>-1250.36</v>
       </c>
       <c r="F23">
-        <v>391.02</v>
+        <v>409.64</v>
       </c>
       <c r="G23">
         <v>420.4</v>
@@ -3167,37 +3167,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M23">
-        <v>57.401736</v>
+        <v>60.13515200000001</v>
       </c>
       <c r="N23">
-        <v>-8.301736000000005</v>
+        <v>-11.03515200000001</v>
       </c>
       <c r="O23">
-        <v>-2.822590240000002</v>
+        <v>-3.751951680000004</v>
       </c>
       <c r="P23">
-        <v>-5.479145760000003</v>
+        <v>-7.283200320000007</v>
       </c>
       <c r="Q23">
-        <v>186.42085424</v>
+        <v>184.61679968</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09517706941070031</v>
+        <v>0.09581010876211955</v>
       </c>
       <c r="T23">
-        <v>0.6435487412433993</v>
+        <v>0.6517993661311352</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.2908274411770403</v>
+        <v>0.2776080120326294</v>
       </c>
       <c r="W23">
-        <v>0.1041065316352105</v>
+        <v>0.10604714383361</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8553748269912951</v>
+        <v>0.8164941530371452</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09806225647784746</v>
+        <v>0.1121746040566724</v>
       </c>
       <c r="C24">
-        <v>1023.621118991575</v>
+        <v>789.6499562474294</v>
       </c>
       <c r="D24">
-        <v>1012.861118991575</v>
+        <v>797.5099562474295</v>
       </c>
       <c r="E24">
-        <v>-1250.36</v>
+        <v>-1231.74</v>
       </c>
       <c r="F24">
-        <v>409.64</v>
+        <v>428.26</v>
       </c>
       <c r="G24">
         <v>420.4</v>
@@ -3249,45 +3249,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M24">
-        <v>60.13515200000001</v>
+        <v>85.994608</v>
       </c>
       <c r="N24">
-        <v>-11.03515200000001</v>
+        <v>-36.89460800000001</v>
       </c>
       <c r="O24">
-        <v>-3.751951680000004</v>
+        <v>-12.54416672</v>
       </c>
       <c r="P24">
-        <v>-7.283200320000007</v>
+        <v>-24.35044128</v>
       </c>
       <c r="Q24">
-        <v>184.61679968</v>
+        <v>167.54955872</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09581010876211955</v>
+        <v>0.09734575638088078</v>
       </c>
       <c r="T24">
-        <v>0.6517993661311352</v>
+        <v>0.6718140025573514</v>
       </c>
       <c r="U24">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.2776080120326294</v>
+        <v>0.1941284504721505</v>
       </c>
       <c r="W24">
-        <v>0.10604714383361</v>
+        <v>0.1618190071451922</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8164941530371452</v>
+        <v>0.5709660308004427</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1121746040566724</v>
+        <v>0.1137246040566724</v>
       </c>
       <c r="C25">
-        <v>789.6499562474294</v>
+        <v>752.8312424035894</v>
       </c>
       <c r="D25">
-        <v>797.5099562474295</v>
+        <v>779.3112424035895</v>
       </c>
       <c r="E25">
-        <v>-1231.74</v>
+        <v>-1213.12</v>
       </c>
       <c r="F25">
-        <v>428.26</v>
+        <v>446.8800000000001</v>
       </c>
       <c r="G25">
         <v>420.4</v>
@@ -3331,37 +3331,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M25">
-        <v>85.994608</v>
+        <v>89.73350400000001</v>
       </c>
       <c r="N25">
-        <v>-36.89460800000001</v>
+        <v>-40.63350400000002</v>
       </c>
       <c r="O25">
-        <v>-12.54416672</v>
+        <v>-13.81539136000001</v>
       </c>
       <c r="P25">
-        <v>-24.35044128</v>
+        <v>-26.81811264000001</v>
       </c>
       <c r="Q25">
-        <v>167.54955872</v>
+        <v>165.08188736</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09734575638088078</v>
+        <v>0.09802399001747131</v>
       </c>
       <c r="T25">
-        <v>0.6718140025573514</v>
+        <v>0.6806536604857376</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1941284504721505</v>
+        <v>0.1860397650358109</v>
       </c>
       <c r="W25">
-        <v>0.1618190071451922</v>
+        <v>0.1634432151808092</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5709660308004427</v>
+        <v>0.5471757795170908</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1137246040566724</v>
+        <v>0.1152746040566724</v>
       </c>
       <c r="C26">
-        <v>752.8312424035895</v>
+        <v>716.8245664789563</v>
       </c>
       <c r="D26">
-        <v>779.3112424035895</v>
+        <v>761.9245664789563</v>
       </c>
       <c r="E26">
-        <v>-1213.12</v>
+        <v>-1194.5</v>
       </c>
       <c r="F26">
-        <v>446.88</v>
+        <v>465.5</v>
       </c>
       <c r="G26">
         <v>420.4</v>
@@ -3413,37 +3413,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M26">
-        <v>89.733504</v>
+        <v>93.47240000000001</v>
       </c>
       <c r="N26">
-        <v>-40.633504</v>
+        <v>-44.37240000000001</v>
       </c>
       <c r="O26">
-        <v>-13.81539136</v>
+        <v>-15.086616</v>
       </c>
       <c r="P26">
-        <v>-26.81811264</v>
+        <v>-29.28578400000001</v>
       </c>
       <c r="Q26">
-        <v>165.08188736</v>
+        <v>162.614216</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09802399001747131</v>
+        <v>0.09872030988437093</v>
       </c>
       <c r="T26">
-        <v>0.6806536604857376</v>
+        <v>0.6897290426255475</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1860397650358109</v>
+        <v>0.1785981744343785</v>
       </c>
       <c r="W26">
-        <v>0.1634432151808091</v>
+        <v>0.1649374865735768</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5471757795170908</v>
+        <v>0.5252887483364073</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1152746040566724</v>
+        <v>0.1168246040566724</v>
       </c>
       <c r="C27">
-        <v>716.8245664789563</v>
+        <v>681.5767641317578</v>
       </c>
       <c r="D27">
-        <v>761.9245664789563</v>
+        <v>745.2967641317579</v>
       </c>
       <c r="E27">
-        <v>-1194.5</v>
+        <v>-1175.88</v>
       </c>
       <c r="F27">
-        <v>465.5</v>
+        <v>484.12</v>
       </c>
       <c r="G27">
         <v>420.4</v>
@@ -3495,37 +3495,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M27">
-        <v>93.47240000000001</v>
+        <v>97.211296</v>
       </c>
       <c r="N27">
-        <v>-44.37240000000001</v>
+        <v>-48.11129600000001</v>
       </c>
       <c r="O27">
-        <v>-15.086616</v>
+        <v>-16.35784064000001</v>
       </c>
       <c r="P27">
-        <v>-29.28578400000001</v>
+        <v>-31.75345536</v>
       </c>
       <c r="Q27">
-        <v>162.614216</v>
+        <v>160.14654464</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09872030988437093</v>
+        <v>0.09943544920713271</v>
       </c>
       <c r="T27">
-        <v>0.6897290426255475</v>
+        <v>0.6990497053637306</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1785981744343785</v>
+        <v>0.1717290138792101</v>
       </c>
       <c r="W27">
-        <v>0.1649374865735768</v>
+        <v>0.1663168140130546</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5252887483364073</v>
+        <v>0.5050853349388531</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1168246040566724</v>
+        <v>0.128099939546573</v>
       </c>
       <c r="C28">
-        <v>681.5767641317578</v>
+        <v>560.8488998803214</v>
       </c>
       <c r="D28">
-        <v>745.2967641317579</v>
+        <v>643.1888998803214</v>
       </c>
       <c r="E28">
-        <v>-1175.88</v>
+        <v>-1157.26</v>
       </c>
       <c r="F28">
-        <v>484.12</v>
+        <v>502.74</v>
       </c>
       <c r="G28">
         <v>420.4</v>
@@ -3577,45 +3577,45 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M28">
-        <v>97.211296</v>
+        <v>118.546092</v>
       </c>
       <c r="N28">
-        <v>-48.11129600000001</v>
+        <v>-69.44609200000001</v>
       </c>
       <c r="O28">
-        <v>-16.35784064000001</v>
+        <v>-23.61167128</v>
       </c>
       <c r="P28">
-        <v>-31.75345536</v>
+        <v>-45.83442072</v>
       </c>
       <c r="Q28">
-        <v>160.14654464</v>
+        <v>146.06557928</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09943544920713271</v>
+        <v>0.1005473532920258</v>
       </c>
       <c r="T28">
-        <v>0.6990497053637306</v>
+        <v>0.7135415430275768</v>
       </c>
       <c r="U28">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1717290138792101</v>
+        <v>0.1408228623850376</v>
       </c>
       <c r="W28">
-        <v>0.1663168140130546</v>
+        <v>0.2025939690496081</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5050853349388531</v>
+        <v>0.4141848893677574</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.128099939546573</v>
+        <v>0.129999939546573</v>
       </c>
       <c r="C29">
-        <v>560.8488998803214</v>
+        <v>527.7151256857845</v>
       </c>
       <c r="D29">
-        <v>643.1888998803214</v>
+        <v>628.6751256857846</v>
       </c>
       <c r="E29">
-        <v>-1157.26</v>
+        <v>-1138.64</v>
       </c>
       <c r="F29">
-        <v>502.74</v>
+        <v>521.36</v>
       </c>
       <c r="G29">
         <v>420.4</v>
@@ -3659,37 +3659,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M29">
-        <v>118.546092</v>
+        <v>122.936688</v>
       </c>
       <c r="N29">
-        <v>-69.44609200000001</v>
+        <v>-73.83668800000001</v>
       </c>
       <c r="O29">
-        <v>-23.61167128</v>
+        <v>-25.10447392</v>
       </c>
       <c r="P29">
-        <v>-45.83442072</v>
+        <v>-48.73221408000001</v>
       </c>
       <c r="Q29">
-        <v>146.06557928</v>
+        <v>143.16778592</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1005473532920258</v>
+        <v>0.1013077331988595</v>
       </c>
       <c r="T29">
-        <v>0.7135415430275768</v>
+        <v>0.723451842236293</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1408228623850376</v>
+        <v>0.1357934744427148</v>
       </c>
       <c r="W29">
-        <v>0.2025939690496081</v>
+        <v>0.2037798987264079</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4141848893677574</v>
+        <v>0.3993925718903375</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.129999939546573</v>
+        <v>0.131899939546573</v>
       </c>
       <c r="C30">
-        <v>527.7151256857845</v>
+        <v>495.2219134037146</v>
       </c>
       <c r="D30">
-        <v>628.6751256857846</v>
+        <v>614.8019134037146</v>
       </c>
       <c r="E30">
-        <v>-1138.64</v>
+        <v>-1120.02</v>
       </c>
       <c r="F30">
-        <v>521.36</v>
+        <v>539.98</v>
       </c>
       <c r="G30">
         <v>420.4</v>
@@ -3741,37 +3741,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M30">
-        <v>122.936688</v>
+        <v>127.327284</v>
       </c>
       <c r="N30">
-        <v>-73.83668800000001</v>
+        <v>-78.22728400000001</v>
       </c>
       <c r="O30">
-        <v>-25.10447392</v>
+        <v>-26.59727656</v>
       </c>
       <c r="P30">
-        <v>-48.73221408000001</v>
+        <v>-51.63000744000001</v>
       </c>
       <c r="Q30">
-        <v>143.16778592</v>
+        <v>140.26999256</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1013077331988595</v>
+        <v>0.1020895322579983</v>
       </c>
       <c r="T30">
-        <v>0.723451842236293</v>
+        <v>0.7336413048030014</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.1357934744427148</v>
+        <v>0.1311109408412418</v>
       </c>
       <c r="W30">
-        <v>0.2037798987264079</v>
+        <v>0.2048840401496352</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3993925718903375</v>
+        <v>0.3856204142389466</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.131899939546573</v>
+        <v>0.133799939546573</v>
       </c>
       <c r="C31">
-        <v>495.2219134037146</v>
+        <v>463.3277720635512</v>
       </c>
       <c r="D31">
-        <v>614.8019134037147</v>
+        <v>601.5277720635512</v>
       </c>
       <c r="E31">
-        <v>-1120.02</v>
+        <v>-1101.4</v>
       </c>
       <c r="F31">
-        <v>539.98</v>
+        <v>558.6</v>
       </c>
       <c r="G31">
         <v>420.4</v>
@@ -3823,37 +3823,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M31">
-        <v>127.327284</v>
+        <v>131.71788</v>
       </c>
       <c r="N31">
-        <v>-78.22728400000001</v>
+        <v>-82.61788000000001</v>
       </c>
       <c r="O31">
-        <v>-26.59727656</v>
+        <v>-28.09007920000001</v>
       </c>
       <c r="P31">
-        <v>-51.63000744000001</v>
+        <v>-54.52780080000001</v>
       </c>
       <c r="Q31">
-        <v>140.26999256</v>
+        <v>137.3721992</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1020895322579983</v>
+        <v>0.1028936684331126</v>
       </c>
       <c r="T31">
-        <v>0.7336413048030014</v>
+        <v>0.7441218948716157</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.1311109408412418</v>
+        <v>0.1267405761465338</v>
       </c>
       <c r="W31">
-        <v>0.2048840401496352</v>
+        <v>0.2059145721446473</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3856204142389466</v>
+        <v>0.3727664004309816</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.133799939546573</v>
+        <v>0.135699939546573</v>
       </c>
       <c r="C32">
-        <v>463.3277720635512</v>
+        <v>431.9947182763608</v>
       </c>
       <c r="D32">
-        <v>601.5277720635512</v>
+        <v>588.8147182763608</v>
       </c>
       <c r="E32">
-        <v>-1101.4</v>
+        <v>-1082.78</v>
       </c>
       <c r="F32">
-        <v>558.6</v>
+        <v>577.22</v>
       </c>
       <c r="G32">
         <v>420.4</v>
@@ -3905,37 +3905,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M32">
-        <v>131.71788</v>
+        <v>136.108476</v>
       </c>
       <c r="N32">
-        <v>-82.61788000000001</v>
+        <v>-87.00847600000003</v>
       </c>
       <c r="O32">
-        <v>-28.09007920000001</v>
+        <v>-29.58288184000001</v>
       </c>
       <c r="P32">
-        <v>-54.52780080000001</v>
+        <v>-57.42559416000002</v>
       </c>
       <c r="Q32">
-        <v>137.3721992</v>
+        <v>134.47440584</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1028936684331126</v>
+        <v>0.1037211129031577</v>
       </c>
       <c r="T32">
-        <v>0.7441218948716157</v>
+        <v>0.7549062701596101</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.1267405761465338</v>
+        <v>0.1226521704643875</v>
       </c>
       <c r="W32">
-        <v>0.2059145721446473</v>
+        <v>0.2068786182044974</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3727664004309816</v>
+        <v>0.3607416778364338</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.135699939546573</v>
+        <v>0.137599939546573</v>
       </c>
       <c r="C33">
-        <v>431.9947182763608</v>
+        <v>401.1879132495718</v>
       </c>
       <c r="D33">
-        <v>588.8147182763608</v>
+        <v>576.6279132495719</v>
       </c>
       <c r="E33">
-        <v>-1082.78</v>
+        <v>-1064.16</v>
       </c>
       <c r="F33">
-        <v>577.22</v>
+        <v>595.84</v>
       </c>
       <c r="G33">
         <v>420.4</v>
@@ -3987,37 +3987,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M33">
-        <v>136.108476</v>
+        <v>140.499072</v>
       </c>
       <c r="N33">
-        <v>-87.00847600000003</v>
+        <v>-91.39907200000002</v>
       </c>
       <c r="O33">
-        <v>-29.58288184000001</v>
+        <v>-31.07568448000001</v>
       </c>
       <c r="P33">
-        <v>-57.42559416000002</v>
+        <v>-60.32338752000001</v>
       </c>
       <c r="Q33">
-        <v>134.47440584</v>
+        <v>131.57661248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1037211129031577</v>
+        <v>0.104572893975263</v>
       </c>
       <c r="T33">
-        <v>0.7549062701596101</v>
+        <v>0.766007832956075</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.1226521704643875</v>
+        <v>0.1188192901373754</v>
       </c>
       <c r="W33">
-        <v>0.2068786182044974</v>
+        <v>0.2077824113856069</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3607416778364338</v>
+        <v>0.3494685004040453</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.137599939546573</v>
+        <v>0.139499939546573</v>
       </c>
       <c r="C34">
-        <v>401.1879132495718</v>
+        <v>370.875343964299</v>
       </c>
       <c r="D34">
-        <v>576.6279132495719</v>
+        <v>564.935343964299</v>
       </c>
       <c r="E34">
-        <v>-1064.16</v>
+        <v>-1045.54</v>
       </c>
       <c r="F34">
-        <v>595.84</v>
+        <v>614.46</v>
       </c>
       <c r="G34">
         <v>420.4</v>
@@ -4069,37 +4069,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M34">
-        <v>140.499072</v>
+        <v>144.889668</v>
       </c>
       <c r="N34">
-        <v>-91.39907200000002</v>
+        <v>-95.78966800000001</v>
       </c>
       <c r="O34">
-        <v>-31.07568448000001</v>
+        <v>-32.56848712000001</v>
       </c>
       <c r="P34">
-        <v>-60.32338752000001</v>
+        <v>-63.22118088</v>
       </c>
       <c r="Q34">
-        <v>131.57661248</v>
+        <v>128.67881912</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.104572893975263</v>
+        <v>0.1054501013480281</v>
       </c>
       <c r="T34">
-        <v>0.766007832956075</v>
+        <v>0.7774407856867627</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1188192901373754</v>
+        <v>0.115218705587758</v>
       </c>
       <c r="W34">
-        <v>0.2077824113856069</v>
+        <v>0.2086314292224067</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3494685004040453</v>
+        <v>0.338878545846347</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.139499939546573</v>
+        <v>0.141399939546573</v>
       </c>
       <c r="C35">
-        <v>370.875343964299</v>
+        <v>341.0275423712942</v>
       </c>
       <c r="D35">
-        <v>564.935343964299</v>
+        <v>553.7075423712943</v>
       </c>
       <c r="E35">
-        <v>-1045.54</v>
+        <v>-1026.92</v>
       </c>
       <c r="F35">
-        <v>614.46</v>
+        <v>633.08</v>
       </c>
       <c r="G35">
         <v>420.4</v>
@@ -4151,37 +4151,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M35">
-        <v>144.889668</v>
+        <v>149.280264</v>
       </c>
       <c r="N35">
-        <v>-95.78966800000001</v>
+        <v>-100.180264</v>
       </c>
       <c r="O35">
-        <v>-32.56848712000001</v>
+        <v>-34.06128976000001</v>
       </c>
       <c r="P35">
-        <v>-63.22118088</v>
+        <v>-66.11897424000001</v>
       </c>
       <c r="Q35">
-        <v>128.67881912</v>
+        <v>125.78102576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1054501013480281</v>
+        <v>0.1063538907623922</v>
       </c>
       <c r="T35">
-        <v>0.7774407856867627</v>
+        <v>0.7892201915305016</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.115218705587758</v>
+        <v>0.1118299201292945</v>
       </c>
       <c r="W35">
-        <v>0.2086314292224067</v>
+        <v>0.2094305048335124</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.338878545846347</v>
+        <v>0.3289115297920426</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.141399939546573</v>
+        <v>0.143299939546573</v>
       </c>
       <c r="C36">
-        <v>341.0275423712942</v>
+        <v>311.6173374193934</v>
       </c>
       <c r="D36">
-        <v>553.7075423712943</v>
+        <v>542.9173374193934</v>
       </c>
       <c r="E36">
-        <v>-1026.92</v>
+        <v>-1008.3</v>
       </c>
       <c r="F36">
-        <v>633.08</v>
+        <v>651.7</v>
       </c>
       <c r="G36">
         <v>420.4</v>
@@ -4233,37 +4233,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M36">
-        <v>149.280264</v>
+        <v>153.67086</v>
       </c>
       <c r="N36">
-        <v>-100.180264</v>
+        <v>-104.57086</v>
       </c>
       <c r="O36">
-        <v>-34.06128976000001</v>
+        <v>-35.55409240000001</v>
       </c>
       <c r="P36">
-        <v>-66.11897424000001</v>
+        <v>-69.01676760000001</v>
       </c>
       <c r="Q36">
-        <v>125.78102576</v>
+        <v>122.8832324</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1063538907623922</v>
+        <v>0.1072854890818136</v>
       </c>
       <c r="T36">
-        <v>0.7892201915305016</v>
+        <v>0.8013620406309708</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.1118299201292945</v>
+        <v>0.1086347795541718</v>
       </c>
       <c r="W36">
-        <v>0.2094305048335124</v>
+        <v>0.2101839189811263</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3289115297920426</v>
+        <v>0.31951405751227</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.143299939546573</v>
+        <v>0.145199939546573</v>
       </c>
       <c r="C37">
-        <v>311.6173374193934</v>
+        <v>282.6196355233724</v>
       </c>
       <c r="D37">
-        <v>542.9173374193934</v>
+        <v>532.5396355233725</v>
       </c>
       <c r="E37">
-        <v>-1008.3</v>
+        <v>-989.6799999999999</v>
       </c>
       <c r="F37">
-        <v>651.7</v>
+        <v>670.3200000000001</v>
       </c>
       <c r="G37">
         <v>420.4</v>
@@ -4315,37 +4315,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M37">
-        <v>153.67086</v>
+        <v>158.061456</v>
       </c>
       <c r="N37">
-        <v>-104.57086</v>
+        <v>-108.961456</v>
       </c>
       <c r="O37">
-        <v>-35.55409240000001</v>
+        <v>-37.04689504000001</v>
       </c>
       <c r="P37">
-        <v>-69.01676760000001</v>
+        <v>-71.91456096000002</v>
       </c>
       <c r="Q37">
-        <v>122.8832324</v>
+        <v>119.98543904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1072854890818136</v>
+        <v>0.1082461998487169</v>
       </c>
       <c r="T37">
-        <v>0.8013620406309708</v>
+        <v>0.8138833225158297</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.1086347795541718</v>
+        <v>0.1056171467887781</v>
       </c>
       <c r="W37">
-        <v>0.2101839189811263</v>
+        <v>0.2108954767872061</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.31951405751227</v>
+        <v>0.310638667025818</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.145199939546573</v>
+        <v>0.147099939546573</v>
       </c>
       <c r="C38">
-        <v>282.6196355233725</v>
+        <v>254.0112257373111</v>
       </c>
       <c r="D38">
-        <v>532.5396355233725</v>
+        <v>522.551225737311</v>
       </c>
       <c r="E38">
-        <v>-989.6800000000001</v>
+        <v>-971.0600000000001</v>
       </c>
       <c r="F38">
-        <v>670.3199999999999</v>
+        <v>688.9399999999999</v>
       </c>
       <c r="G38">
         <v>420.4</v>
@@ -4397,37 +4397,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M38">
-        <v>158.061456</v>
+        <v>162.452052</v>
       </c>
       <c r="N38">
-        <v>-108.961456</v>
+        <v>-113.352052</v>
       </c>
       <c r="O38">
-        <v>-37.04689504</v>
+        <v>-38.53969768</v>
       </c>
       <c r="P38">
-        <v>-71.91456095999999</v>
+        <v>-74.81235432</v>
       </c>
       <c r="Q38">
-        <v>119.98543904</v>
+        <v>117.08764568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1082461998487169</v>
+        <v>0.1092374093701251</v>
       </c>
       <c r="T38">
-        <v>0.8138833225158296</v>
+        <v>0.8268021054129064</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.1056171467887782</v>
+        <v>0.1027626293080004</v>
       </c>
       <c r="W38">
-        <v>0.2108954767872061</v>
+        <v>0.2115685720091735</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3106386670258181</v>
+        <v>0.3022430273764717</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.147099939546573</v>
+        <v>0.148999939546573</v>
       </c>
       <c r="C39">
-        <v>254.0112257373111</v>
+        <v>225.7706064495175</v>
       </c>
       <c r="D39">
-        <v>522.551225737311</v>
+        <v>512.9306064495175</v>
       </c>
       <c r="E39">
-        <v>-971.0600000000001</v>
+        <v>-952.4399999999999</v>
       </c>
       <c r="F39">
-        <v>688.9399999999999</v>
+        <v>707.5600000000001</v>
       </c>
       <c r="G39">
         <v>420.4</v>
@@ -4479,37 +4479,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M39">
-        <v>162.452052</v>
+        <v>166.842648</v>
       </c>
       <c r="N39">
-        <v>-113.352052</v>
+        <v>-117.742648</v>
       </c>
       <c r="O39">
-        <v>-38.53969768</v>
+        <v>-40.03250032000001</v>
       </c>
       <c r="P39">
-        <v>-74.81235432</v>
+        <v>-77.71014768000002</v>
       </c>
       <c r="Q39">
-        <v>117.08764568</v>
+        <v>114.18985232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1092374093701251</v>
+        <v>0.1102605933922239</v>
       </c>
       <c r="T39">
-        <v>0.8268021054129064</v>
+        <v>0.8401376232421469</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.1027626293080004</v>
+        <v>0.1000583495893688</v>
       </c>
       <c r="W39">
-        <v>0.2115685720091735</v>
+        <v>0.2122062411668268</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3022430273764717</v>
+        <v>0.2942892634981434</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.148999939546573</v>
+        <v>0.150899939546573</v>
       </c>
       <c r="C40">
-        <v>225.7706064495175</v>
+        <v>197.8778308755388</v>
       </c>
       <c r="D40">
-        <v>512.9306064495175</v>
+        <v>503.657830875539</v>
       </c>
       <c r="E40">
-        <v>-952.4399999999999</v>
+        <v>-933.8199999999999</v>
       </c>
       <c r="F40">
-        <v>707.5600000000001</v>
+        <v>726.1800000000001</v>
       </c>
       <c r="G40">
         <v>420.4</v>
@@ -4561,37 +4561,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M40">
-        <v>166.842648</v>
+        <v>171.233244</v>
       </c>
       <c r="N40">
-        <v>-117.742648</v>
+        <v>-122.133244</v>
       </c>
       <c r="O40">
-        <v>-40.03250032000001</v>
+        <v>-41.52530296000001</v>
       </c>
       <c r="P40">
-        <v>-77.71014768000002</v>
+        <v>-80.60794104000001</v>
       </c>
       <c r="Q40">
-        <v>114.18985232</v>
+        <v>111.29205896</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1102605933922239</v>
+        <v>0.1113173244314407</v>
       </c>
       <c r="T40">
-        <v>0.8401376232421469</v>
+        <v>0.8539103711641491</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.1000583495893688</v>
+        <v>0.09749275088194906</v>
       </c>
       <c r="W40">
-        <v>0.2122062411668268</v>
+        <v>0.2128112093420364</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2942892634981434</v>
+        <v>0.286743384946909</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.150899939546573</v>
+        <v>0.152799939546573</v>
       </c>
       <c r="C41">
-        <v>197.8778308755388</v>
+        <v>170.314369012675</v>
       </c>
       <c r="D41">
-        <v>503.657830875539</v>
+        <v>494.7143690126751</v>
       </c>
       <c r="E41">
-        <v>-933.8199999999999</v>
+        <v>-915.1999999999999</v>
       </c>
       <c r="F41">
-        <v>726.1800000000001</v>
+        <v>744.8000000000001</v>
       </c>
       <c r="G41">
         <v>420.4</v>
@@ -4643,37 +4643,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M41">
-        <v>171.233244</v>
+        <v>175.62384</v>
       </c>
       <c r="N41">
-        <v>-122.133244</v>
+        <v>-126.52384</v>
       </c>
       <c r="O41">
-        <v>-41.52530296000001</v>
+        <v>-43.01810560000001</v>
       </c>
       <c r="P41">
-        <v>-80.60794104000001</v>
+        <v>-83.50573440000002</v>
       </c>
       <c r="Q41">
-        <v>111.29205896</v>
+        <v>108.3942656</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1113173244314407</v>
+        <v>0.1124092798386314</v>
       </c>
       <c r="T41">
-        <v>0.8539103711641491</v>
+        <v>0.8681422106835518</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.09749275088194906</v>
+        <v>0.09505543210990032</v>
       </c>
       <c r="W41">
-        <v>0.2128112093420364</v>
+        <v>0.2133859291084855</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.286743384946909</v>
+        <v>0.2795748003232362</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.152799939546573</v>
+        <v>0.154699939546573</v>
       </c>
       <c r="C42">
-        <v>170.314369012675</v>
+        <v>143.062984045541</v>
       </c>
       <c r="D42">
-        <v>494.7143690126751</v>
+        <v>486.0829840455412</v>
       </c>
       <c r="E42">
-        <v>-915.1999999999999</v>
+        <v>-896.5799999999999</v>
       </c>
       <c r="F42">
-        <v>744.8000000000001</v>
+        <v>763.4200000000001</v>
       </c>
       <c r="G42">
         <v>420.4</v>
@@ -4725,37 +4725,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M42">
-        <v>175.62384</v>
+        <v>180.014436</v>
       </c>
       <c r="N42">
-        <v>-126.52384</v>
+        <v>-130.914436</v>
       </c>
       <c r="O42">
-        <v>-43.01810560000001</v>
+        <v>-44.51090824000001</v>
       </c>
       <c r="P42">
-        <v>-83.50573440000002</v>
+        <v>-86.40352776</v>
       </c>
       <c r="Q42">
-        <v>108.3942656</v>
+        <v>105.49647224</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1124092798386314</v>
+        <v>0.1135382506833539</v>
       </c>
       <c r="T42">
-        <v>0.8681422106835518</v>
+        <v>0.8828564854409</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.09505543210990032</v>
+        <v>0.09273700693648813</v>
       </c>
       <c r="W42">
-        <v>0.2133859291084855</v>
+        <v>0.2139326137643761</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2795748003232362</v>
+        <v>0.2727559027543768</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.154699939546573</v>
+        <v>0.156599939546573</v>
       </c>
       <c r="C43">
-        <v>143.062984045541</v>
+        <v>116.1076214680342</v>
       </c>
       <c r="D43">
-        <v>486.0829840455412</v>
+        <v>477.7476214680342</v>
       </c>
       <c r="E43">
-        <v>-896.5799999999999</v>
+        <v>-877.9599999999999</v>
       </c>
       <c r="F43">
-        <v>763.4200000000001</v>
+        <v>782.0400000000001</v>
       </c>
       <c r="G43">
         <v>420.4</v>
@@ -4807,37 +4807,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M43">
-        <v>180.014436</v>
+        <v>184.405032</v>
       </c>
       <c r="N43">
-        <v>-130.914436</v>
+        <v>-135.305032</v>
       </c>
       <c r="O43">
-        <v>-44.51090824000001</v>
+        <v>-46.00371088000001</v>
       </c>
       <c r="P43">
-        <v>-86.40352776</v>
+        <v>-89.30132112000003</v>
       </c>
       <c r="Q43">
-        <v>105.49647224</v>
+        <v>102.59867888</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1135382506833539</v>
+        <v>0.1147061515572049</v>
       </c>
       <c r="T43">
-        <v>0.8828564854409</v>
+        <v>0.8980781489829845</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.09273700693648813</v>
+        <v>0.09052898296180983</v>
       </c>
       <c r="W43">
-        <v>0.2139326137643761</v>
+        <v>0.2144532658176052</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2727559027543768</v>
+        <v>0.2662617145935583</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.156599939546573</v>
+        <v>0.158499939546573</v>
       </c>
       <c r="C44">
-        <v>116.1076214680343</v>
+        <v>89.43330942100658</v>
       </c>
       <c r="D44">
-        <v>477.7476214680342</v>
+        <v>469.6933094210066</v>
       </c>
       <c r="E44">
-        <v>-877.96</v>
+        <v>-859.34</v>
       </c>
       <c r="F44">
-        <v>782.04</v>
+        <v>800.66</v>
       </c>
       <c r="G44">
         <v>420.4</v>
@@ -4889,37 +4889,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M44">
-        <v>184.405032</v>
+        <v>188.795628</v>
       </c>
       <c r="N44">
-        <v>-135.305032</v>
+        <v>-139.695628</v>
       </c>
       <c r="O44">
-        <v>-46.00371088000001</v>
+        <v>-47.49651352</v>
       </c>
       <c r="P44">
-        <v>-89.30132112000001</v>
+        <v>-92.19911447999999</v>
       </c>
       <c r="Q44">
-        <v>102.59867888</v>
+        <v>99.70088552000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1147061515572048</v>
+        <v>0.1159150314090856</v>
       </c>
       <c r="T44">
-        <v>0.8980781489829844</v>
+        <v>0.9138339059826859</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.09052898296180985</v>
+        <v>0.08842365777665147</v>
       </c>
       <c r="W44">
-        <v>0.2144532658176052</v>
+        <v>0.2149497014962656</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2662617145935583</v>
+        <v>0.2600695816960338</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.158499939546573</v>
+        <v>0.160399939546573</v>
       </c>
       <c r="C45">
-        <v>89.43330942100658</v>
+        <v>63.02606894399696</v>
       </c>
       <c r="D45">
-        <v>469.6933094210066</v>
+        <v>461.906068943997</v>
       </c>
       <c r="E45">
-        <v>-859.34</v>
+        <v>-840.72</v>
       </c>
       <c r="F45">
-        <v>800.66</v>
+        <v>819.28</v>
       </c>
       <c r="G45">
         <v>420.4</v>
@@ -4971,37 +4971,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M45">
-        <v>188.795628</v>
+        <v>193.186224</v>
       </c>
       <c r="N45">
-        <v>-139.695628</v>
+        <v>-144.086224</v>
       </c>
       <c r="O45">
-        <v>-47.49651352</v>
+        <v>-48.98931616000001</v>
       </c>
       <c r="P45">
-        <v>-92.19911447999999</v>
+        <v>-95.09690784</v>
       </c>
       <c r="Q45">
-        <v>99.70088552000001</v>
+        <v>96.80309216000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1159150314090856</v>
+        <v>0.1171670855413907</v>
       </c>
       <c r="T45">
-        <v>0.9138339059826859</v>
+        <v>0.9301523685895197</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08842365777665147</v>
+        <v>0.08641402919081848</v>
       </c>
       <c r="W45">
-        <v>0.2149497014962656</v>
+        <v>0.215423571916805</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2600695816960338</v>
+        <v>0.2541589093847603</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.160399939546573</v>
+        <v>0.162299939546573</v>
       </c>
       <c r="C46">
-        <v>63.02606894399696</v>
+        <v>36.87283300920285</v>
       </c>
       <c r="D46">
-        <v>461.906068943997</v>
+        <v>454.3728330092029</v>
       </c>
       <c r="E46">
-        <v>-840.72</v>
+        <v>-822.1</v>
       </c>
       <c r="F46">
-        <v>819.28</v>
+        <v>837.9</v>
       </c>
       <c r="G46">
         <v>420.4</v>
@@ -5053,37 +5053,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M46">
-        <v>193.186224</v>
+        <v>197.57682</v>
       </c>
       <c r="N46">
-        <v>-144.086224</v>
+        <v>-148.47682</v>
       </c>
       <c r="O46">
-        <v>-48.98931616000001</v>
+        <v>-50.4821188</v>
       </c>
       <c r="P46">
-        <v>-95.09690784</v>
+        <v>-97.99470120000001</v>
       </c>
       <c r="Q46">
-        <v>96.80309216000001</v>
+        <v>93.9052988</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1171670855413907</v>
+        <v>0.1184646689148706</v>
       </c>
       <c r="T46">
-        <v>0.9301523685895197</v>
+        <v>0.9470642298366018</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.08641402919081848</v>
+        <v>0.08449371743102252</v>
       </c>
       <c r="W46">
-        <v>0.215423571916805</v>
+        <v>0.2158763814297649</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2541589093847603</v>
+        <v>0.2485109336206545</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.162299939546573</v>
+        <v>0.164199939546573</v>
       </c>
       <c r="C47">
-        <v>36.87283300920285</v>
+        <v>10.96137335116896</v>
       </c>
       <c r="D47">
-        <v>454.3728330092029</v>
+        <v>447.081373351169</v>
       </c>
       <c r="E47">
-        <v>-822.1</v>
+        <v>-803.48</v>
       </c>
       <c r="F47">
-        <v>837.9</v>
+        <v>856.52</v>
       </c>
       <c r="G47">
         <v>420.4</v>
@@ -5135,37 +5135,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M47">
-        <v>197.57682</v>
+        <v>201.967416</v>
       </c>
       <c r="N47">
-        <v>-148.47682</v>
+        <v>-152.867416</v>
       </c>
       <c r="O47">
-        <v>-50.4821188</v>
+        <v>-51.97492144000001</v>
       </c>
       <c r="P47">
-        <v>-97.99470120000001</v>
+        <v>-100.89249456</v>
       </c>
       <c r="Q47">
-        <v>93.9052988</v>
+        <v>91.00750543999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1184646689148706</v>
+        <v>0.1198103109318126</v>
       </c>
       <c r="T47">
-        <v>0.9470642298366018</v>
+        <v>0.9646024563150574</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08449371743102252</v>
+        <v>0.08265689748686986</v>
       </c>
       <c r="W47">
-        <v>0.2158763814297649</v>
+        <v>0.2163095035725961</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2485109336206545</v>
+        <v>0.2431085220202054</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.164199939546573</v>
+        <v>0.166099939546573</v>
       </c>
       <c r="C48">
-        <v>10.96137335116896</v>
+        <v>-14.71976576967302</v>
       </c>
       <c r="D48">
-        <v>447.081373351169</v>
+        <v>440.0202342303271</v>
       </c>
       <c r="E48">
-        <v>-803.48</v>
+        <v>-784.8599999999999</v>
       </c>
       <c r="F48">
-        <v>856.52</v>
+        <v>875.1400000000001</v>
       </c>
       <c r="G48">
         <v>420.4</v>
@@ -5217,37 +5217,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M48">
-        <v>201.967416</v>
+        <v>206.358012</v>
       </c>
       <c r="N48">
-        <v>-152.867416</v>
+        <v>-157.258012</v>
       </c>
       <c r="O48">
-        <v>-51.97492144000001</v>
+        <v>-53.46772408000002</v>
       </c>
       <c r="P48">
-        <v>-100.89249456</v>
+        <v>-103.79028792</v>
       </c>
       <c r="Q48">
-        <v>91.00750543999999</v>
+        <v>88.10971207999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1198103109318126</v>
+        <v>0.1212067318927902</v>
       </c>
       <c r="T48">
-        <v>0.9646024563150574</v>
+        <v>0.9828025026606246</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08265689748686986</v>
+        <v>0.08089824009353219</v>
       </c>
       <c r="W48">
-        <v>0.2163095035725961</v>
+        <v>0.2167241949859451</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2431085220202054</v>
+        <v>0.2379360002750947</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.166099939546573</v>
+        <v>0.167999939546573</v>
       </c>
       <c r="C49">
-        <v>-14.71976576967302</v>
+        <v>-40.18132762428411</v>
       </c>
       <c r="D49">
-        <v>440.0202342303271</v>
+        <v>433.178672375716</v>
       </c>
       <c r="E49">
-        <v>-784.8599999999999</v>
+        <v>-766.2399999999999</v>
       </c>
       <c r="F49">
-        <v>875.1400000000001</v>
+        <v>893.7600000000001</v>
       </c>
       <c r="G49">
         <v>420.4</v>
@@ -5299,37 +5299,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M49">
-        <v>206.358012</v>
+        <v>210.748608</v>
       </c>
       <c r="N49">
-        <v>-157.258012</v>
+        <v>-161.6486080000001</v>
       </c>
       <c r="O49">
-        <v>-53.46772408000002</v>
+        <v>-54.96052672000002</v>
       </c>
       <c r="P49">
-        <v>-103.79028792</v>
+        <v>-106.68808128</v>
       </c>
       <c r="Q49">
-        <v>88.10971207999998</v>
+        <v>85.21191871999997</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1212067318927902</v>
+        <v>0.1226568613522669</v>
       </c>
       <c r="T49">
-        <v>0.9828025026606246</v>
+        <v>1.001702550788713</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08089824009353219</v>
+        <v>0.0792128600915836</v>
       </c>
       <c r="W49">
-        <v>0.2167241949859451</v>
+        <v>0.2171216075904046</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2379360002750947</v>
+        <v>0.2329790002693635</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.167999939546573</v>
+        <v>0.169899939546573</v>
       </c>
       <c r="C50">
-        <v>-40.18132762428399</v>
+        <v>-65.43339755534942</v>
       </c>
       <c r="D50">
-        <v>433.178672375716</v>
+        <v>426.5466024446505</v>
       </c>
       <c r="E50">
-        <v>-766.24</v>
+        <v>-747.62</v>
       </c>
       <c r="F50">
-        <v>893.76</v>
+        <v>912.38</v>
       </c>
       <c r="G50">
         <v>420.4</v>
@@ -5381,37 +5381,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M50">
-        <v>210.748608</v>
+        <v>215.139204</v>
       </c>
       <c r="N50">
-        <v>-161.648608</v>
+        <v>-166.039204</v>
       </c>
       <c r="O50">
-        <v>-54.96052672000001</v>
+        <v>-56.45332936000001</v>
       </c>
       <c r="P50">
-        <v>-106.68808128</v>
+        <v>-109.58587464</v>
       </c>
       <c r="Q50">
-        <v>85.21191872</v>
+        <v>82.31412535999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1226568613522669</v>
+        <v>0.124163858633684</v>
       </c>
       <c r="T50">
-        <v>1.001702550788713</v>
+        <v>1.021343777274767</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0792128600915836</v>
+        <v>0.07759627111012272</v>
       </c>
       <c r="W50">
-        <v>0.2171216075904046</v>
+        <v>0.2175027992722331</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2329790002693636</v>
+        <v>0.2282243267944786</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.169899939546573</v>
+        <v>0.171799939546573</v>
       </c>
       <c r="C51">
-        <v>-65.43339755534942</v>
+        <v>-90.4854525830051</v>
       </c>
       <c r="D51">
-        <v>426.5466024446505</v>
+        <v>420.114547416995</v>
       </c>
       <c r="E51">
-        <v>-747.62</v>
+        <v>-729</v>
       </c>
       <c r="F51">
-        <v>912.38</v>
+        <v>931</v>
       </c>
       <c r="G51">
         <v>420.4</v>
@@ -5463,37 +5463,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M51">
-        <v>215.139204</v>
+        <v>219.5298</v>
       </c>
       <c r="N51">
-        <v>-166.039204</v>
+        <v>-170.4298</v>
       </c>
       <c r="O51">
-        <v>-56.45332936000001</v>
+        <v>-57.94613200000001</v>
       </c>
       <c r="P51">
-        <v>-109.58587464</v>
+        <v>-112.483668</v>
       </c>
       <c r="Q51">
-        <v>82.31412535999999</v>
+        <v>79.41633199999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.124163858633684</v>
+        <v>0.1257311358063576</v>
       </c>
       <c r="T51">
-        <v>1.021343777274767</v>
+        <v>1.041770652820262</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07759627111012272</v>
+        <v>0.07604434568792026</v>
       </c>
       <c r="W51">
-        <v>0.2175027992722331</v>
+        <v>0.2178687432867884</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2282243267944786</v>
+        <v>0.223659840258589</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.171799939546573</v>
+        <v>0.173699939546573</v>
       </c>
       <c r="C52">
-        <v>-90.4854525830051</v>
+        <v>-115.3464065890986</v>
       </c>
       <c r="D52">
-        <v>420.114547416995</v>
+        <v>413.8735934109015</v>
       </c>
       <c r="E52">
-        <v>-729</v>
+        <v>-710.38</v>
       </c>
       <c r="F52">
-        <v>931</v>
+        <v>949.62</v>
       </c>
       <c r="G52">
         <v>420.4</v>
@@ -5545,37 +5545,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M52">
-        <v>219.5298</v>
+        <v>223.920396</v>
       </c>
       <c r="N52">
-        <v>-170.4298</v>
+        <v>-174.820396</v>
       </c>
       <c r="O52">
-        <v>-57.94613200000001</v>
+        <v>-59.43893464000001</v>
       </c>
       <c r="P52">
-        <v>-112.483668</v>
+        <v>-115.38146136</v>
       </c>
       <c r="Q52">
-        <v>79.41633199999998</v>
+        <v>76.51853864</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1257311358063576</v>
+        <v>0.1273623834758751</v>
       </c>
       <c r="T52">
-        <v>1.041770652820262</v>
+        <v>1.063031278388022</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07604434568792026</v>
+        <v>0.07455328008619634</v>
       </c>
       <c r="W52">
-        <v>0.2178687432867884</v>
+        <v>0.2182203365556749</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.223659840258589</v>
+        <v>0.2192743531946951</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.173699939546573</v>
+        <v>0.175599939546573</v>
       </c>
       <c r="C53">
-        <v>-115.3464065890986</v>
+        <v>-140.0246515330307</v>
       </c>
       <c r="D53">
-        <v>413.8735934109015</v>
+        <v>407.8153484669694</v>
       </c>
       <c r="E53">
-        <v>-710.38</v>
+        <v>-691.76</v>
       </c>
       <c r="F53">
-        <v>949.62</v>
+        <v>968.24</v>
       </c>
       <c r="G53">
         <v>420.4</v>
@@ -5627,37 +5627,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M53">
-        <v>223.920396</v>
+        <v>228.310992</v>
       </c>
       <c r="N53">
-        <v>-174.820396</v>
+        <v>-179.210992</v>
       </c>
       <c r="O53">
-        <v>-59.43893464000001</v>
+        <v>-60.93173728000001</v>
       </c>
       <c r="P53">
-        <v>-115.38146136</v>
+        <v>-118.27925472</v>
       </c>
       <c r="Q53">
-        <v>76.51853864</v>
+        <v>73.62074528000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1273623834758751</v>
+        <v>0.1290615997982892</v>
       </c>
       <c r="T53">
-        <v>1.063031278388022</v>
+        <v>1.08517776335444</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07455328008619634</v>
+        <v>0.0731195631614618</v>
       </c>
       <c r="W53">
-        <v>0.2182203365556749</v>
+        <v>0.2185584070065273</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2192743531946951</v>
+        <v>0.2150575387101817</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.175599939546573</v>
+        <v>0.177499939546573</v>
       </c>
       <c r="C54">
-        <v>-140.0246515330307</v>
+        <v>-164.528095099937</v>
       </c>
       <c r="D54">
-        <v>407.8153484669694</v>
+        <v>401.931904900063</v>
       </c>
       <c r="E54">
-        <v>-691.76</v>
+        <v>-673.14</v>
       </c>
       <c r="F54">
-        <v>968.24</v>
+        <v>986.86</v>
       </c>
       <c r="G54">
         <v>420.4</v>
@@ -5709,37 +5709,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M54">
-        <v>228.310992</v>
+        <v>232.701588</v>
       </c>
       <c r="N54">
-        <v>-179.210992</v>
+        <v>-183.601588</v>
       </c>
       <c r="O54">
-        <v>-60.93173728000001</v>
+        <v>-62.42453992000002</v>
       </c>
       <c r="P54">
-        <v>-118.27925472</v>
+        <v>-121.17704808</v>
       </c>
       <c r="Q54">
-        <v>73.62074528000001</v>
+        <v>70.72295192</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1290615997982892</v>
+        <v>0.1308331231982528</v>
       </c>
       <c r="T54">
-        <v>1.08517776335444</v>
+        <v>1.108266651936449</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.0731195631614618</v>
+        <v>0.07173994876218892</v>
       </c>
       <c r="W54">
-        <v>0.2185584070065273</v>
+        <v>0.2188837200818759</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2150575387101817</v>
+        <v>0.2109998493005557</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.177499939546573</v>
+        <v>0.179399939546573</v>
       </c>
       <c r="C55">
-        <v>-164.528095099937</v>
+        <v>-188.8641951363736</v>
       </c>
       <c r="D55">
-        <v>401.931904900063</v>
+        <v>396.2158048636264</v>
       </c>
       <c r="E55">
-        <v>-673.14</v>
+        <v>-654.52</v>
       </c>
       <c r="F55">
-        <v>986.86</v>
+        <v>1005.48</v>
       </c>
       <c r="G55">
         <v>420.4</v>
@@ -5791,37 +5791,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M55">
-        <v>232.701588</v>
+        <v>237.092184</v>
       </c>
       <c r="N55">
-        <v>-183.601588</v>
+        <v>-187.992184</v>
       </c>
       <c r="O55">
-        <v>-62.42453992000002</v>
+        <v>-63.91734256000001</v>
       </c>
       <c r="P55">
-        <v>-121.17704808</v>
+        <v>-124.07484144</v>
       </c>
       <c r="Q55">
-        <v>70.72295192</v>
+        <v>67.82515856000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1308331231982528</v>
+        <v>0.1326816693547365</v>
       </c>
       <c r="T55">
-        <v>1.108266651936449</v>
+        <v>1.132359405239415</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07173994876218892</v>
+        <v>0.07041143119251878</v>
       </c>
       <c r="W55">
-        <v>0.2188837200818759</v>
+        <v>0.2191969845248041</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2109998493005557</v>
+        <v>0.2070924446838787</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.179399939546573</v>
+        <v>0.181299939546573</v>
       </c>
       <c r="C56">
-        <v>-188.8641951363736</v>
+        <v>-213.0399911888298</v>
       </c>
       <c r="D56">
-        <v>396.2158048636264</v>
+        <v>390.6600088111703</v>
       </c>
       <c r="E56">
-        <v>-654.52</v>
+        <v>-635.8999999999999</v>
       </c>
       <c r="F56">
-        <v>1005.48</v>
+        <v>1024.1</v>
       </c>
       <c r="G56">
         <v>420.4</v>
@@ -5873,37 +5873,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M56">
-        <v>237.092184</v>
+        <v>241.48278</v>
       </c>
       <c r="N56">
-        <v>-187.992184</v>
+        <v>-192.3827800000001</v>
       </c>
       <c r="O56">
-        <v>-63.91734256000001</v>
+        <v>-65.41014520000002</v>
       </c>
       <c r="P56">
-        <v>-124.07484144</v>
+        <v>-126.9726348</v>
       </c>
       <c r="Q56">
-        <v>67.82515856000001</v>
+        <v>64.92736519999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1326816693547365</v>
+        <v>0.1346123731181752</v>
       </c>
       <c r="T56">
-        <v>1.132359405239415</v>
+        <v>1.157522947578069</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07041143119251878</v>
+        <v>0.06913122335265477</v>
       </c>
       <c r="W56">
-        <v>0.2191969845248041</v>
+        <v>0.219498857533444</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2070924446838787</v>
+        <v>0.2033271275078081</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.181299939546573</v>
+        <v>0.183199939546573</v>
       </c>
       <c r="C57">
-        <v>-213.0399911888298</v>
+        <v>-237.0621334255056</v>
       </c>
       <c r="D57">
-        <v>390.6600088111703</v>
+        <v>385.2578665744945</v>
       </c>
       <c r="E57">
-        <v>-635.8999999999999</v>
+        <v>-617.28</v>
       </c>
       <c r="F57">
-        <v>1024.1</v>
+        <v>1042.72</v>
       </c>
       <c r="G57">
         <v>420.4</v>
@@ -5955,37 +5955,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M57">
-        <v>241.48278</v>
+        <v>245.873376</v>
       </c>
       <c r="N57">
-        <v>-192.3827800000001</v>
+        <v>-196.773376</v>
       </c>
       <c r="O57">
-        <v>-65.41014520000002</v>
+        <v>-66.90294784000001</v>
       </c>
       <c r="P57">
-        <v>-126.9726348</v>
+        <v>-129.87042816</v>
       </c>
       <c r="Q57">
-        <v>64.92736519999997</v>
+        <v>62.02957183999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1346123731181752</v>
+        <v>0.1366308361435882</v>
       </c>
       <c r="T57">
-        <v>1.157522947578069</v>
+        <v>1.183830287295752</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06913122335265477</v>
+        <v>0.06789673722135738</v>
       </c>
       <c r="W57">
-        <v>0.219498857533444</v>
+        <v>0.219789949363204</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2033271275078081</v>
+        <v>0.1996962859451687</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.183199939546573</v>
+        <v>0.185099939546573</v>
       </c>
       <c r="C58">
-        <v>-237.0621334255056</v>
+        <v>-260.9369091911965</v>
       </c>
       <c r="D58">
-        <v>385.2578665744945</v>
+        <v>380.0030908088037</v>
       </c>
       <c r="E58">
-        <v>-617.28</v>
+        <v>-598.6599999999999</v>
       </c>
       <c r="F58">
-        <v>1042.72</v>
+        <v>1061.34</v>
       </c>
       <c r="G58">
         <v>420.4</v>
@@ -6037,37 +6037,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M58">
-        <v>245.873376</v>
+        <v>250.2639720000001</v>
       </c>
       <c r="N58">
-        <v>-196.773376</v>
+        <v>-201.1639720000001</v>
       </c>
       <c r="O58">
-        <v>-66.90294784000001</v>
+        <v>-68.39575048000002</v>
       </c>
       <c r="P58">
-        <v>-129.87042816</v>
+        <v>-132.7682215200001</v>
       </c>
       <c r="Q58">
-        <v>62.02957183999999</v>
+        <v>59.13177847999995</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1366308361435882</v>
+        <v>0.1387431811701833</v>
       </c>
       <c r="T58">
-        <v>1.183830287295752</v>
+        <v>1.211361224209607</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06789673722135738</v>
+        <v>0.0667055663929125</v>
       </c>
       <c r="W58">
-        <v>0.219789949363204</v>
+        <v>0.2200708274445513</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1996962859451687</v>
+        <v>0.1961928423320956</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.185099939546573</v>
+        <v>0.186999939546573</v>
       </c>
       <c r="C59">
-        <v>-260.9369091911965</v>
+        <v>-284.6702674182272</v>
       </c>
       <c r="D59">
-        <v>380.0030908088037</v>
+        <v>374.8897325817728</v>
       </c>
       <c r="E59">
-        <v>-598.6599999999999</v>
+        <v>-580.04</v>
       </c>
       <c r="F59">
-        <v>1061.34</v>
+        <v>1079.96</v>
       </c>
       <c r="G59">
         <v>420.4</v>
@@ -6119,37 +6119,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M59">
-        <v>250.2639720000001</v>
+        <v>254.654568</v>
       </c>
       <c r="N59">
-        <v>-201.1639720000001</v>
+        <v>-205.554568</v>
       </c>
       <c r="O59">
-        <v>-68.39575048000002</v>
+        <v>-69.88855312000001</v>
       </c>
       <c r="P59">
-        <v>-132.7682215200001</v>
+        <v>-135.66601488</v>
       </c>
       <c r="Q59">
-        <v>59.13177847999995</v>
+        <v>56.23398512</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1387431811701833</v>
+        <v>0.1409561140551877</v>
       </c>
       <c r="T59">
-        <v>1.211361224209607</v>
+        <v>1.24020315811936</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.0667055663929125</v>
+        <v>0.06555547042062092</v>
       </c>
       <c r="W59">
-        <v>0.2200708274445513</v>
+        <v>0.2203420200748176</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1961928423320956</v>
+        <v>0.1928102071194733</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.186999939546573</v>
+        <v>0.188899939546573</v>
       </c>
       <c r="C60">
-        <v>-284.6702674182272</v>
+        <v>-308.2678410926978</v>
       </c>
       <c r="D60">
-        <v>374.8897325817728</v>
+        <v>369.9121589073022</v>
       </c>
       <c r="E60">
-        <v>-580.04</v>
+        <v>-561.4200000000001</v>
       </c>
       <c r="F60">
-        <v>1079.96</v>
+        <v>1098.58</v>
       </c>
       <c r="G60">
         <v>420.4</v>
@@ -6201,37 +6201,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M60">
-        <v>254.654568</v>
+        <v>259.045164</v>
       </c>
       <c r="N60">
-        <v>-205.554568</v>
+        <v>-209.945164</v>
       </c>
       <c r="O60">
-        <v>-69.88855312000001</v>
+        <v>-71.38135576000001</v>
       </c>
       <c r="P60">
-        <v>-135.66601488</v>
+        <v>-138.56380824</v>
       </c>
       <c r="Q60">
-        <v>56.23398512</v>
+        <v>53.33619175999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1409561140551877</v>
+        <v>0.143276994885802</v>
       </c>
       <c r="T60">
-        <v>1.240203158119359</v>
+        <v>1.270452015634466</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06555547042062092</v>
+        <v>0.06444436075247481</v>
       </c>
       <c r="W60">
-        <v>0.2203420200748176</v>
+        <v>0.2206040197345664</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1928102071194733</v>
+        <v>0.1895422375072788</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.188899939546573</v>
+        <v>0.190799939546573</v>
       </c>
       <c r="C61">
-        <v>-308.2678410926978</v>
+        <v>-331.7349679544172</v>
       </c>
       <c r="D61">
-        <v>369.9121589073022</v>
+        <v>365.0650320455829</v>
       </c>
       <c r="E61">
-        <v>-561.4200000000001</v>
+        <v>-542.8</v>
       </c>
       <c r="F61">
-        <v>1098.58</v>
+        <v>1117.2</v>
       </c>
       <c r="G61">
         <v>420.4</v>
@@ -6283,37 +6283,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M61">
-        <v>259.045164</v>
+        <v>263.43576</v>
       </c>
       <c r="N61">
-        <v>-209.945164</v>
+        <v>-214.33576</v>
       </c>
       <c r="O61">
-        <v>-71.38135576000001</v>
+        <v>-72.87415840000001</v>
       </c>
       <c r="P61">
-        <v>-138.56380824</v>
+        <v>-141.4616016</v>
       </c>
       <c r="Q61">
-        <v>53.33619175999999</v>
+        <v>50.43839840000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.143276994885802</v>
+        <v>0.145713919757947</v>
       </c>
       <c r="T61">
-        <v>1.270452015634466</v>
+        <v>1.302213316025327</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06444436075247481</v>
+        <v>0.06337028807326689</v>
       </c>
       <c r="W61">
-        <v>0.2206040197345664</v>
+        <v>0.2208572860723237</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1895422375072788</v>
+        <v>0.1863832002154908</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.190799939546573</v>
+        <v>0.192699939546573</v>
       </c>
       <c r="C62">
-        <v>-331.7349679544172</v>
+        <v>-355.0767095904421</v>
       </c>
       <c r="D62">
-        <v>365.0650320455829</v>
+        <v>360.3432904095578</v>
       </c>
       <c r="E62">
-        <v>-542.8</v>
+        <v>-524.1800000000001</v>
       </c>
       <c r="F62">
-        <v>1117.2</v>
+        <v>1135.82</v>
       </c>
       <c r="G62">
         <v>420.4</v>
@@ -6365,37 +6365,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M62">
-        <v>263.43576</v>
+        <v>267.826356</v>
       </c>
       <c r="N62">
-        <v>-214.33576</v>
+        <v>-218.726356</v>
       </c>
       <c r="O62">
-        <v>-72.87415840000001</v>
+        <v>-74.36696103999999</v>
       </c>
       <c r="P62">
-        <v>-141.4616016</v>
+        <v>-144.35939496</v>
       </c>
       <c r="Q62">
-        <v>50.43839840000001</v>
+        <v>47.54060504000003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.145713919757947</v>
+        <v>0.1482758151363559</v>
       </c>
       <c r="T62">
-        <v>1.302213316025327</v>
+        <v>1.335603401051618</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06337028807326689</v>
+        <v>0.06233143089173793</v>
       </c>
       <c r="W62">
-        <v>0.2208572860723237</v>
+        <v>0.2211022485957282</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1863832002154908</v>
+        <v>0.1833277379168763</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.192699939546573</v>
+        <v>0.194599939546573</v>
       </c>
       <c r="C63">
-        <v>-355.0767095904421</v>
+        <v>-378.2978690658052</v>
       </c>
       <c r="D63">
-        <v>360.3432904095578</v>
+        <v>355.7421309341948</v>
       </c>
       <c r="E63">
-        <v>-524.1800000000001</v>
+        <v>-505.5599999999999</v>
       </c>
       <c r="F63">
-        <v>1135.82</v>
+        <v>1154.44</v>
       </c>
       <c r="G63">
         <v>420.4</v>
@@ -6447,37 +6447,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M63">
-        <v>267.826356</v>
+        <v>272.216952</v>
       </c>
       <c r="N63">
-        <v>-218.726356</v>
+        <v>-223.1169520000001</v>
       </c>
       <c r="O63">
-        <v>-74.36696103999999</v>
+        <v>-75.85976368000003</v>
       </c>
       <c r="P63">
-        <v>-144.35939496</v>
+        <v>-147.25718832</v>
       </c>
       <c r="Q63">
-        <v>47.54060504000003</v>
+        <v>44.64281167999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1482758151363559</v>
+        <v>0.1509725471136285</v>
       </c>
       <c r="T63">
-        <v>1.335603401051618</v>
+        <v>1.370750858974029</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06233143089173793</v>
+        <v>0.06132608523219376</v>
       </c>
       <c r="W63">
-        <v>0.2211022485957282</v>
+        <v>0.2213393091022487</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1833277379168763</v>
+        <v>0.1803708389182169</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.194599939546573</v>
+        <v>0.196499939546573</v>
       </c>
       <c r="C64">
-        <v>-378.2978690658052</v>
+        <v>-401.4030072205294</v>
       </c>
       <c r="D64">
-        <v>355.7421309341948</v>
+        <v>351.2569927794706</v>
       </c>
       <c r="E64">
-        <v>-505.5599999999999</v>
+        <v>-486.9400000000001</v>
       </c>
       <c r="F64">
-        <v>1154.44</v>
+        <v>1173.06</v>
       </c>
       <c r="G64">
         <v>420.4</v>
@@ -6529,37 +6529,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M64">
-        <v>272.216952</v>
+        <v>276.607548</v>
       </c>
       <c r="N64">
-        <v>-223.1169520000001</v>
+        <v>-227.507548</v>
       </c>
       <c r="O64">
-        <v>-75.85976368000003</v>
+        <v>-77.35256632000001</v>
       </c>
       <c r="P64">
-        <v>-147.25718832</v>
+        <v>-150.15498168</v>
       </c>
       <c r="Q64">
-        <v>44.64281167999999</v>
+        <v>41.74501832000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1509725471136285</v>
+        <v>0.1538150483869698</v>
       </c>
       <c r="T64">
-        <v>1.370750858974029</v>
+        <v>1.40779817948684</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06132608523219376</v>
+        <v>0.06035265530787323</v>
       </c>
       <c r="W64">
-        <v>0.2213393091022487</v>
+        <v>0.2215688438784035</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1803708389182169</v>
+        <v>0.1775078097290389</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.196499939546573</v>
+        <v>0.198399939546573</v>
       </c>
       <c r="C65">
-        <v>-401.4030072205294</v>
+        <v>-424.3964577491736</v>
       </c>
       <c r="D65">
-        <v>351.2569927794706</v>
+        <v>346.8835422508265</v>
       </c>
       <c r="E65">
-        <v>-486.9400000000001</v>
+        <v>-468.3199999999999</v>
       </c>
       <c r="F65">
-        <v>1173.06</v>
+        <v>1191.68</v>
       </c>
       <c r="G65">
         <v>420.4</v>
@@ -6611,37 +6611,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M65">
-        <v>276.607548</v>
+        <v>280.998144</v>
       </c>
       <c r="N65">
-        <v>-227.507548</v>
+        <v>-231.898144</v>
       </c>
       <c r="O65">
-        <v>-77.35256632000001</v>
+        <v>-78.84536896000002</v>
       </c>
       <c r="P65">
-        <v>-150.15498168</v>
+        <v>-153.05277504</v>
       </c>
       <c r="Q65">
-        <v>41.74501832000001</v>
+        <v>38.84722495999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1538150483869698</v>
+        <v>0.1568154663977189</v>
       </c>
       <c r="T65">
-        <v>1.40779817948684</v>
+        <v>1.446903684472586</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06035265530787323</v>
+        <v>0.05940964506868771</v>
       </c>
       <c r="W65">
-        <v>0.2215688438784035</v>
+        <v>0.2217912056928034</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1775078097290389</v>
+        <v>0.1747342502020226</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.198399939546573</v>
+        <v>0.200299939546573</v>
       </c>
       <c r="C66">
-        <v>-424.3964577491736</v>
+        <v>-447.2823411677095</v>
       </c>
       <c r="D66">
-        <v>346.8835422508265</v>
+        <v>342.6176588322905</v>
       </c>
       <c r="E66">
-        <v>-468.3199999999999</v>
+        <v>-449.7</v>
       </c>
       <c r="F66">
-        <v>1191.68</v>
+        <v>1210.3</v>
       </c>
       <c r="G66">
         <v>420.4</v>
@@ -6693,37 +6693,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M66">
-        <v>280.998144</v>
+        <v>285.38874</v>
       </c>
       <c r="N66">
-        <v>-231.898144</v>
+        <v>-236.28874</v>
       </c>
       <c r="O66">
-        <v>-78.84536896000002</v>
+        <v>-80.3381716</v>
       </c>
       <c r="P66">
-        <v>-153.05277504</v>
+        <v>-155.9505684</v>
       </c>
       <c r="Q66">
-        <v>38.84722495999998</v>
+        <v>35.9494316</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1568154663977189</v>
+        <v>0.1599873368662252</v>
       </c>
       <c r="T66">
-        <v>1.446903684472586</v>
+        <v>1.488243789743231</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05940964506868771</v>
+        <v>0.05849565052916945</v>
       </c>
       <c r="W66">
-        <v>0.2217912056928034</v>
+        <v>0.2220067256052218</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1747342502020226</v>
+        <v>0.1720460309681454</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.200299939546573</v>
+        <v>0.202199939546573</v>
       </c>
       <c r="C67">
-        <v>-447.2823411677095</v>
+        <v>-470.0645777623569</v>
       </c>
       <c r="D67">
-        <v>342.6176588322905</v>
+        <v>338.4554222376432</v>
       </c>
       <c r="E67">
-        <v>-449.7</v>
+        <v>-431.0799999999999</v>
       </c>
       <c r="F67">
-        <v>1210.3</v>
+        <v>1228.92</v>
       </c>
       <c r="G67">
         <v>420.4</v>
@@ -6775,37 +6775,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M67">
-        <v>285.38874</v>
+        <v>289.779336</v>
       </c>
       <c r="N67">
-        <v>-236.28874</v>
+        <v>-240.679336</v>
       </c>
       <c r="O67">
-        <v>-80.3381716</v>
+        <v>-81.83097424</v>
       </c>
       <c r="P67">
-        <v>-155.9505684</v>
+        <v>-158.84836176</v>
       </c>
       <c r="Q67">
-        <v>35.9494316</v>
+        <v>33.05163824000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1599873368662252</v>
+        <v>0.1633457879505259</v>
       </c>
       <c r="T67">
-        <v>1.488243789743231</v>
+        <v>1.53201566591215</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05849565052916945</v>
+        <v>0.05760935279387899</v>
       </c>
       <c r="W67">
-        <v>0.2220067256052218</v>
+        <v>0.2222157146112033</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1720460309681454</v>
+        <v>0.1694392729231735</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.202199939546573</v>
+        <v>0.204099939546573</v>
       </c>
       <c r="C68">
-        <v>-470.0645777623569</v>
+        <v>-492.7468996058994</v>
       </c>
       <c r="D68">
-        <v>338.4554222376432</v>
+        <v>334.3931003941006</v>
       </c>
       <c r="E68">
-        <v>-431.0799999999999</v>
+        <v>-412.46</v>
       </c>
       <c r="F68">
-        <v>1228.92</v>
+        <v>1247.54</v>
       </c>
       <c r="G68">
         <v>420.4</v>
@@ -6857,37 +6857,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M68">
-        <v>289.779336</v>
+        <v>294.169932</v>
       </c>
       <c r="N68">
-        <v>-240.679336</v>
+        <v>-245.069932</v>
       </c>
       <c r="O68">
-        <v>-81.83097424</v>
+        <v>-83.32377688000001</v>
       </c>
       <c r="P68">
-        <v>-158.84836176</v>
+        <v>-161.74615512</v>
       </c>
       <c r="Q68">
-        <v>33.05163824000002</v>
+        <v>30.15384487999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1633457879505259</v>
+        <v>0.1669077815247843</v>
       </c>
       <c r="T68">
-        <v>1.53201566591215</v>
+        <v>1.578440383061003</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05760935279387899</v>
+        <v>0.05674951170740318</v>
       </c>
       <c r="W68">
-        <v>0.2222157146112033</v>
+        <v>0.2224184651393943</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1694392729231735</v>
+        <v>0.1669103285511858</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.204099939546573</v>
+        <v>0.2059999395465731</v>
       </c>
       <c r="C69">
-        <v>-492.7468996058994</v>
+        <v>-515.3328617189131</v>
       </c>
       <c r="D69">
-        <v>334.3931003941006</v>
+        <v>330.4271382810869</v>
       </c>
       <c r="E69">
-        <v>-412.46</v>
+        <v>-393.8399999999999</v>
       </c>
       <c r="F69">
-        <v>1247.54</v>
+        <v>1266.16</v>
       </c>
       <c r="G69">
         <v>420.4</v>
@@ -6939,37 +6939,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M69">
-        <v>294.169932</v>
+        <v>298.560528</v>
       </c>
       <c r="N69">
-        <v>-245.069932</v>
+        <v>-249.460528</v>
       </c>
       <c r="O69">
-        <v>-83.32377688000001</v>
+        <v>-84.81657952000002</v>
       </c>
       <c r="P69">
-        <v>-161.74615512</v>
+        <v>-164.64394848</v>
       </c>
       <c r="Q69">
-        <v>30.15384487999998</v>
+        <v>27.25605152</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1669077815247843</v>
+        <v>0.1706923996974338</v>
       </c>
       <c r="T69">
-        <v>1.578440383061003</v>
+        <v>1.62776664503166</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05674951170740318</v>
+        <v>0.05591496006464725</v>
       </c>
       <c r="W69">
-        <v>0.2224184651393943</v>
+        <v>0.2226152524167562</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1669103285511858</v>
+        <v>0.1644557648960213</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2059999395465731</v>
+        <v>0.207899939546573</v>
       </c>
       <c r="C70">
-        <v>-515.3328617189131</v>
+        <v>-537.8258524460548</v>
       </c>
       <c r="D70">
-        <v>330.4271382810869</v>
+        <v>326.5541475539455</v>
       </c>
       <c r="E70">
-        <v>-393.8399999999999</v>
+        <v>-375.2199999999998</v>
       </c>
       <c r="F70">
-        <v>1266.16</v>
+        <v>1284.78</v>
       </c>
       <c r="G70">
         <v>420.4</v>
@@ -7021,37 +7021,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M70">
-        <v>298.560528</v>
+        <v>302.951124</v>
       </c>
       <c r="N70">
-        <v>-249.460528</v>
+        <v>-253.8511240000001</v>
       </c>
       <c r="O70">
-        <v>-84.81657952000002</v>
+        <v>-86.30938216000003</v>
       </c>
       <c r="P70">
-        <v>-164.64394848</v>
+        <v>-167.54174184</v>
       </c>
       <c r="Q70">
-        <v>27.25605152</v>
+        <v>24.35825815999996</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1706923996974338</v>
+        <v>0.1747211867844478</v>
       </c>
       <c r="T70">
-        <v>1.62776664503166</v>
+        <v>1.680275246484294</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05591496006464725</v>
+        <v>0.0551045983245799</v>
       </c>
       <c r="W70">
-        <v>0.2226152524167562</v>
+        <v>0.2228063357150641</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1644557648960213</v>
+        <v>0.1620723480134703</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.207899939546573</v>
+        <v>0.2097999395465731</v>
       </c>
       <c r="C71">
-        <v>-537.8258524460548</v>
+        <v>-560.2291031110728</v>
       </c>
       <c r="D71">
-        <v>326.5541475539455</v>
+        <v>322.7708968889273</v>
       </c>
       <c r="E71">
-        <v>-375.2199999999998</v>
+        <v>-356.5999999999999</v>
       </c>
       <c r="F71">
-        <v>1284.78</v>
+        <v>1303.4</v>
       </c>
       <c r="G71">
         <v>420.4</v>
@@ -7103,37 +7103,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M71">
-        <v>302.951124</v>
+        <v>307.34172</v>
       </c>
       <c r="N71">
-        <v>-253.8511240000001</v>
+        <v>-258.24172</v>
       </c>
       <c r="O71">
-        <v>-86.30938216000003</v>
+        <v>-87.80218480000001</v>
       </c>
       <c r="P71">
-        <v>-167.54174184</v>
+        <v>-170.4395352</v>
       </c>
       <c r="Q71">
-        <v>24.35825815999996</v>
+        <v>21.46046480000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1747211867844478</v>
+        <v>0.1790185596772627</v>
       </c>
       <c r="T71">
-        <v>1.680275246484294</v>
+        <v>1.736284421367104</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0551045983245799</v>
+        <v>0.05431738977708591</v>
       </c>
       <c r="W71">
-        <v>0.2228063357150641</v>
+        <v>0.2229919594905632</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1620723480134703</v>
+        <v>0.1597570287561351</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2097999395465731</v>
+        <v>0.2116999395465731</v>
       </c>
       <c r="C72">
-        <v>-560.2291031110728</v>
+        <v>-582.5456970083649</v>
       </c>
       <c r="D72">
-        <v>322.7708968889273</v>
+        <v>319.0743029916354</v>
       </c>
       <c r="E72">
-        <v>-356.5999999999999</v>
+        <v>-337.9799999999998</v>
       </c>
       <c r="F72">
-        <v>1303.4</v>
+        <v>1322.02</v>
       </c>
       <c r="G72">
         <v>420.4</v>
@@ -7185,37 +7185,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M72">
-        <v>307.34172</v>
+        <v>311.7323160000001</v>
       </c>
       <c r="N72">
-        <v>-258.24172</v>
+        <v>-262.6323160000001</v>
       </c>
       <c r="O72">
-        <v>-87.80218480000001</v>
+        <v>-89.29498744000003</v>
       </c>
       <c r="P72">
-        <v>-170.4395352</v>
+        <v>-173.33732856</v>
       </c>
       <c r="Q72">
-        <v>21.46046480000004</v>
+        <v>18.56267143999997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1790185596772627</v>
+        <v>0.1836123031144098</v>
       </c>
       <c r="T72">
-        <v>1.736284421367104</v>
+        <v>1.79615629796597</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05431738977708591</v>
+        <v>0.05355235611825369</v>
       </c>
       <c r="W72">
-        <v>0.2229919594905632</v>
+        <v>0.2231723544273158</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1597570287561351</v>
+        <v>0.1575069297595698</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.211699939546573</v>
+        <v>0.213599939546573</v>
       </c>
       <c r="C73">
-        <v>-582.5456970083644</v>
+        <v>-604.7785777836632</v>
       </c>
       <c r="D73">
-        <v>319.0743029916356</v>
+        <v>315.4614222163366</v>
       </c>
       <c r="E73">
-        <v>-337.98</v>
+        <v>-319.3600000000001</v>
       </c>
       <c r="F73">
-        <v>1322.02</v>
+        <v>1340.64</v>
       </c>
       <c r="G73">
         <v>420.4</v>
@@ -7267,37 +7267,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M73">
-        <v>311.732316</v>
+        <v>316.122912</v>
       </c>
       <c r="N73">
-        <v>-262.6323160000001</v>
+        <v>-267.022912</v>
       </c>
       <c r="O73">
-        <v>-89.29498744000003</v>
+        <v>-90.78779008000001</v>
       </c>
       <c r="P73">
-        <v>-173.33732856</v>
+        <v>-176.23512192</v>
       </c>
       <c r="Q73">
-        <v>18.56267143999997</v>
+        <v>15.66487807999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1836123031144097</v>
+        <v>0.1885341710827815</v>
       </c>
       <c r="T73">
-        <v>1.796156297965969</v>
+        <v>1.860304737179039</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0535523561182537</v>
+        <v>0.05280857339438908</v>
       </c>
       <c r="W73">
-        <v>0.2231723544273158</v>
+        <v>0.2233477383936031</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1575069297595696</v>
+        <v>0.1553193335129089</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.213599939546573</v>
+        <v>0.215499939546573</v>
       </c>
       <c r="C74">
-        <v>-604.7785777836632</v>
+        <v>-626.9305572517321</v>
       </c>
       <c r="D74">
-        <v>315.4614222163366</v>
+        <v>311.9294427482678</v>
       </c>
       <c r="E74">
-        <v>-319.3600000000001</v>
+        <v>-300.74</v>
       </c>
       <c r="F74">
-        <v>1340.64</v>
+        <v>1359.26</v>
       </c>
       <c r="G74">
         <v>420.4</v>
@@ -7349,37 +7349,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M74">
-        <v>316.122912</v>
+        <v>320.513508</v>
       </c>
       <c r="N74">
-        <v>-267.022912</v>
+        <v>-271.413508</v>
       </c>
       <c r="O74">
-        <v>-90.78779008000001</v>
+        <v>-92.28059272</v>
       </c>
       <c r="P74">
-        <v>-176.23512192</v>
+        <v>-179.13291528</v>
       </c>
       <c r="Q74">
-        <v>15.66487807999999</v>
+        <v>12.76708472000004</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1885341710827815</v>
+        <v>0.1938206218636252</v>
       </c>
       <c r="T74">
-        <v>1.860304737179039</v>
+        <v>1.929204912630115</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05280857339438908</v>
+        <v>0.05208516827939745</v>
       </c>
       <c r="W74">
-        <v>0.2233477383936031</v>
+        <v>0.2235183173197181</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1553193335129089</v>
+        <v>0.1531916714099926</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.215499939546573</v>
+        <v>0.217399939546573</v>
       </c>
       <c r="C75">
-        <v>-626.9305572517321</v>
+        <v>-649.0043226947022</v>
       </c>
       <c r="D75">
-        <v>311.9294427482678</v>
+        <v>308.4756773052977</v>
       </c>
       <c r="E75">
-        <v>-300.74</v>
+        <v>-282.1200000000001</v>
       </c>
       <c r="F75">
-        <v>1359.26</v>
+        <v>1377.88</v>
       </c>
       <c r="G75">
         <v>420.4</v>
@@ -7431,37 +7431,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M75">
-        <v>320.513508</v>
+        <v>324.904104</v>
       </c>
       <c r="N75">
-        <v>-271.413508</v>
+        <v>-275.8041039999999</v>
       </c>
       <c r="O75">
-        <v>-92.28059272</v>
+        <v>-93.77339535999998</v>
       </c>
       <c r="P75">
-        <v>-179.13291528</v>
+        <v>-182.0307086399999</v>
       </c>
       <c r="Q75">
-        <v>12.76708472000004</v>
+        <v>9.869291360000062</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1938206218636252</v>
+        <v>0.1995137227045339</v>
       </c>
       <c r="T75">
-        <v>1.929204912630115</v>
+        <v>2.003405101577427</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05208516827939745</v>
+        <v>0.05138131465400019</v>
       </c>
       <c r="W75">
-        <v>0.2235183173197181</v>
+        <v>0.2236842860045868</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1531916714099926</v>
+        <v>0.1511215136882359</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.217399939546573</v>
+        <v>0.219299939546573</v>
       </c>
       <c r="C76">
-        <v>-649.0043226947022</v>
+        <v>-671.002443680864</v>
       </c>
       <c r="D76">
-        <v>308.4756773052977</v>
+        <v>305.097556319136</v>
       </c>
       <c r="E76">
-        <v>-282.1200000000001</v>
+        <v>-263.5</v>
       </c>
       <c r="F76">
-        <v>1377.88</v>
+        <v>1396.5</v>
       </c>
       <c r="G76">
         <v>420.4</v>
@@ -7513,37 +7513,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M76">
-        <v>324.904104</v>
+        <v>329.2947</v>
       </c>
       <c r="N76">
-        <v>-275.8041039999999</v>
+        <v>-280.1947</v>
       </c>
       <c r="O76">
-        <v>-93.77339535999998</v>
+        <v>-95.26619800000002</v>
       </c>
       <c r="P76">
-        <v>-182.0307086399999</v>
+        <v>-184.928502</v>
       </c>
       <c r="Q76">
-        <v>9.869291360000062</v>
+        <v>6.971498000000025</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1995137227045339</v>
+        <v>0.2056622716127153</v>
       </c>
       <c r="T76">
-        <v>2.003405101577427</v>
+        <v>2.083541305640524</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05138131465400019</v>
+        <v>0.0506962304586135</v>
       </c>
       <c r="W76">
-        <v>0.2236842860045868</v>
+        <v>0.2238458288578589</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1511215136882359</v>
+        <v>0.1491065601723928</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.219299939546573</v>
+        <v>0.221199939546573</v>
       </c>
       <c r="C77">
-        <v>-671.002443680864</v>
+        <v>-692.9273784402769</v>
       </c>
       <c r="D77">
-        <v>305.097556319136</v>
+        <v>301.7926215597233</v>
       </c>
       <c r="E77">
-        <v>-263.5</v>
+        <v>-244.8799999999999</v>
       </c>
       <c r="F77">
-        <v>1396.5</v>
+        <v>1415.12</v>
       </c>
       <c r="G77">
         <v>420.4</v>
@@ -7595,37 +7595,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M77">
-        <v>329.2947</v>
+        <v>333.6852960000001</v>
       </c>
       <c r="N77">
-        <v>-280.1947</v>
+        <v>-284.5852960000001</v>
       </c>
       <c r="O77">
-        <v>-95.26619800000002</v>
+        <v>-96.75900064000004</v>
       </c>
       <c r="P77">
-        <v>-184.928502</v>
+        <v>-187.82629536</v>
       </c>
       <c r="Q77">
-        <v>6.971498000000025</v>
+        <v>4.07370463999996</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2056622716127153</v>
+        <v>0.2123231995965784</v>
       </c>
       <c r="T77">
-        <v>2.083541305640524</v>
+        <v>2.170355526708879</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0506962304586135</v>
+        <v>0.05002917479468438</v>
       </c>
       <c r="W77">
-        <v>0.2238458288578589</v>
+        <v>0.2240031205834134</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1491065601723928</v>
+        <v>0.1471446317490717</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.221199939546573</v>
+        <v>0.223099939546573</v>
       </c>
       <c r="C78">
-        <v>-692.9273784402769</v>
+        <v>-714.7814798304403</v>
       </c>
       <c r="D78">
-        <v>301.7926215597233</v>
+        <v>298.5585201695598</v>
       </c>
       <c r="E78">
-        <v>-244.8799999999999</v>
+        <v>-226.26</v>
       </c>
       <c r="F78">
-        <v>1415.12</v>
+        <v>1433.74</v>
       </c>
       <c r="G78">
         <v>420.4</v>
@@ -7677,37 +7677,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M78">
-        <v>333.6852960000001</v>
+        <v>338.075892</v>
       </c>
       <c r="N78">
-        <v>-284.5852960000001</v>
+        <v>-288.975892</v>
       </c>
       <c r="O78">
-        <v>-96.75900064000004</v>
+        <v>-98.25180328000002</v>
       </c>
       <c r="P78">
-        <v>-187.82629536</v>
+        <v>-190.72408872</v>
       </c>
       <c r="Q78">
-        <v>4.07370463999996</v>
+        <v>1.17591127999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2123231995965784</v>
+        <v>0.2195633387094731</v>
       </c>
       <c r="T78">
-        <v>2.170355526708879</v>
+        <v>2.264718810478831</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05002917479468438</v>
+        <v>0.04937944525189628</v>
       </c>
       <c r="W78">
-        <v>0.2240031205834134</v>
+        <v>0.2241563268096029</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1471446317490717</v>
+        <v>0.1452336625055772</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.223099939546573</v>
+        <v>0.224999939546573</v>
       </c>
       <c r="C79">
-        <v>-714.7814798304403</v>
+        <v>-736.5670009224536</v>
       </c>
       <c r="D79">
-        <v>298.5585201695598</v>
+        <v>295.3929990775466</v>
       </c>
       <c r="E79">
-        <v>-226.26</v>
+        <v>-207.6399999999999</v>
       </c>
       <c r="F79">
-        <v>1433.74</v>
+        <v>1452.36</v>
       </c>
       <c r="G79">
         <v>420.4</v>
@@ -7759,37 +7759,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M79">
-        <v>338.075892</v>
+        <v>342.466488</v>
       </c>
       <c r="N79">
-        <v>-288.975892</v>
+        <v>-293.366488</v>
       </c>
       <c r="O79">
-        <v>-98.25180328000002</v>
+        <v>-99.74460592000001</v>
       </c>
       <c r="P79">
-        <v>-190.72408872</v>
+        <v>-193.62188208</v>
       </c>
       <c r="Q79">
-        <v>1.17591127999998</v>
+        <v>-1.721882079999972</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2195633387094731</v>
+        <v>0.2274616722871765</v>
       </c>
       <c r="T79">
-        <v>2.264718810478831</v>
+        <v>2.367660574591504</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04937944525189628</v>
+        <v>0.04874637544097453</v>
       </c>
       <c r="W79">
-        <v>0.2241563268096029</v>
+        <v>0.2243056046710182</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1452336625055772</v>
+        <v>0.1433716924734546</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.224999939546573</v>
+        <v>0.2268999395465731</v>
       </c>
       <c r="C80">
-        <v>-736.5670009224536</v>
+        <v>-758.2861002355319</v>
       </c>
       <c r="D80">
-        <v>295.3929990775466</v>
+        <v>292.2938997644681</v>
       </c>
       <c r="E80">
-        <v>-207.6399999999999</v>
+        <v>-189.02</v>
       </c>
       <c r="F80">
-        <v>1452.36</v>
+        <v>1470.98</v>
       </c>
       <c r="G80">
         <v>420.4</v>
@@ -7841,37 +7841,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M80">
-        <v>342.466488</v>
+        <v>346.857084</v>
       </c>
       <c r="N80">
-        <v>-293.366488</v>
+        <v>-297.7570840000001</v>
       </c>
       <c r="O80">
-        <v>-99.74460592000001</v>
+        <v>-101.23740856</v>
       </c>
       <c r="P80">
-        <v>-193.62188208</v>
+        <v>-196.51967544</v>
       </c>
       <c r="Q80">
-        <v>-1.721882079999972</v>
+        <v>-4.619675440000037</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2274616722871765</v>
+        <v>0.2361122281103754</v>
       </c>
       <c r="T80">
-        <v>2.367660574591504</v>
+        <v>2.48040631623872</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04874637544097453</v>
+        <v>0.04812933271387358</v>
       </c>
       <c r="W80">
-        <v>0.2243056046710182</v>
+        <v>0.2244511033460686</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1433716924734546</v>
+        <v>0.1415568609231576</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2268999395465731</v>
+        <v>0.228799939546573</v>
       </c>
       <c r="C81">
-        <v>-758.2861002355319</v>
+        <v>-779.9408466454408</v>
       </c>
       <c r="D81">
-        <v>292.2938997644681</v>
+        <v>289.2591533545594</v>
       </c>
       <c r="E81">
-        <v>-189.02</v>
+        <v>-170.3999999999999</v>
       </c>
       <c r="F81">
-        <v>1470.98</v>
+        <v>1489.6</v>
       </c>
       <c r="G81">
         <v>420.4</v>
@@ -7923,37 +7923,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M81">
-        <v>346.857084</v>
+        <v>351.2476800000001</v>
       </c>
       <c r="N81">
-        <v>-297.7570840000001</v>
+        <v>-302.14768</v>
       </c>
       <c r="O81">
-        <v>-101.23740856</v>
+        <v>-102.7302112</v>
       </c>
       <c r="P81">
-        <v>-196.51967544</v>
+        <v>-199.4174688</v>
       </c>
       <c r="Q81">
-        <v>-4.619675440000037</v>
+        <v>-7.517468800000017</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2361122281103754</v>
+        <v>0.2456278395158941</v>
       </c>
       <c r="T81">
-        <v>2.48040631623872</v>
+        <v>2.604426632050655</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04812933271387358</v>
+        <v>0.04752771605495016</v>
       </c>
       <c r="W81">
-        <v>0.2244511033460686</v>
+        <v>0.2245929645542427</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1415568609231576</v>
+        <v>0.1397874001616182</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.228799939546573</v>
+        <v>0.230699939546573</v>
       </c>
       <c r="C82">
-        <v>-779.9408466454408</v>
+        <v>-801.5332239902978</v>
       </c>
       <c r="D82">
-        <v>289.2591533545594</v>
+        <v>286.2867760097024</v>
       </c>
       <c r="E82">
-        <v>-170.3999999999999</v>
+        <v>-151.78</v>
       </c>
       <c r="F82">
-        <v>1489.6</v>
+        <v>1508.22</v>
       </c>
       <c r="G82">
         <v>420.4</v>
@@ -8005,37 +8005,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M82">
-        <v>351.2476800000001</v>
+        <v>355.638276</v>
       </c>
       <c r="N82">
-        <v>-302.14768</v>
+        <v>-306.538276</v>
       </c>
       <c r="O82">
-        <v>-102.7302112</v>
+        <v>-104.22301384</v>
       </c>
       <c r="P82">
-        <v>-199.4174688</v>
+        <v>-202.31526216</v>
       </c>
       <c r="Q82">
-        <v>-7.517468800000017</v>
+        <v>-10.41526215999997</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2456278395158941</v>
+        <v>0.256145094227257</v>
       </c>
       <c r="T82">
-        <v>2.604426632050655</v>
+        <v>2.741501717948059</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04752771605495016</v>
+        <v>0.04694095412834584</v>
       </c>
       <c r="W82">
-        <v>0.2245929645542427</v>
+        <v>0.2247313230165361</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1397874001616182</v>
+        <v>0.1380616297892525</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.230699939546573</v>
+        <v>0.232599939546573</v>
       </c>
       <c r="C83">
-        <v>-801.5332239902978</v>
+        <v>-823.0651353952951</v>
       </c>
       <c r="D83">
-        <v>286.2867760097024</v>
+        <v>283.3748646047051</v>
       </c>
       <c r="E83">
-        <v>-151.78</v>
+        <v>-133.1599999999999</v>
       </c>
       <c r="F83">
-        <v>1508.22</v>
+        <v>1526.84</v>
       </c>
       <c r="G83">
         <v>420.4</v>
@@ -8087,37 +8087,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M83">
-        <v>355.638276</v>
+        <v>360.028872</v>
       </c>
       <c r="N83">
-        <v>-306.538276</v>
+        <v>-310.9288720000001</v>
       </c>
       <c r="O83">
-        <v>-104.22301384</v>
+        <v>-105.71581648</v>
       </c>
       <c r="P83">
-        <v>-202.31526216</v>
+        <v>-205.21305552</v>
       </c>
       <c r="Q83">
-        <v>-10.41526215999997</v>
+        <v>-13.31305552000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.256145094227257</v>
+        <v>0.267830932795438</v>
       </c>
       <c r="T83">
-        <v>2.741501717948059</v>
+        <v>2.893807368945173</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04694095412834584</v>
+        <v>0.04636850346824407</v>
       </c>
       <c r="W83">
-        <v>0.2247313230165361</v>
+        <v>0.2248663068821881</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1380616297892525</v>
+        <v>0.1363779513771883</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.232599939546573</v>
+        <v>0.234499939546573</v>
       </c>
       <c r="C84">
-        <v>-823.0651353952951</v>
+        <v>-844.5384073361481</v>
       </c>
       <c r="D84">
-        <v>283.3748646047051</v>
+        <v>280.5215926638519</v>
       </c>
       <c r="E84">
-        <v>-133.1599999999999</v>
+        <v>-114.54</v>
       </c>
       <c r="F84">
-        <v>1526.84</v>
+        <v>1545.46</v>
       </c>
       <c r="G84">
         <v>420.4</v>
@@ -8169,37 +8169,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M84">
-        <v>360.028872</v>
+        <v>364.4194680000001</v>
       </c>
       <c r="N84">
-        <v>-310.9288720000001</v>
+        <v>-315.319468</v>
       </c>
       <c r="O84">
-        <v>-105.71581648</v>
+        <v>-107.20861912</v>
       </c>
       <c r="P84">
-        <v>-205.21305552</v>
+        <v>-208.11084888</v>
       </c>
       <c r="Q84">
-        <v>-13.31305552000003</v>
+        <v>-16.21084887999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.267830932795438</v>
+        <v>0.280891575901052</v>
       </c>
       <c r="T84">
-        <v>2.893807368945173</v>
+        <v>3.064031331824301</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04636850346824407</v>
+        <v>0.04580984679995197</v>
       </c>
       <c r="W84">
-        <v>0.2248663068821881</v>
+        <v>0.2249980381245713</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1363779513771883</v>
+        <v>0.1347348435292706</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.234499939546573</v>
+        <v>0.236399939546573</v>
       </c>
       <c r="C85">
-        <v>-844.5384073361481</v>
+        <v>-865.9547934595084</v>
       </c>
       <c r="D85">
-        <v>280.5215926638519</v>
+        <v>277.7252065404918</v>
       </c>
       <c r="E85">
-        <v>-114.54</v>
+        <v>-95.91999999999985</v>
       </c>
       <c r="F85">
-        <v>1545.46</v>
+        <v>1564.08</v>
       </c>
       <c r="G85">
         <v>420.4</v>
@@ -8251,37 +8251,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M85">
-        <v>364.4194680000001</v>
+        <v>368.8100640000001</v>
       </c>
       <c r="N85">
-        <v>-315.319468</v>
+        <v>-319.7100640000001</v>
       </c>
       <c r="O85">
-        <v>-107.20861912</v>
+        <v>-108.70142176</v>
       </c>
       <c r="P85">
-        <v>-208.11084888</v>
+        <v>-211.0086422400001</v>
       </c>
       <c r="Q85">
-        <v>-16.21084887999999</v>
+        <v>-19.10864224000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.280891575901052</v>
+        <v>0.2955847993948677</v>
       </c>
       <c r="T85">
-        <v>3.064031331824301</v>
+        <v>3.25553329006332</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04580984679995197</v>
+        <v>0.04526449148090492</v>
       </c>
       <c r="W85">
-        <v>0.2249980381245713</v>
+        <v>0.2251266329088026</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1347348435292706</v>
+        <v>0.1331308572967791</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.236399939546573</v>
+        <v>0.238299939546573</v>
       </c>
       <c r="C86">
-        <v>-865.9547934595082</v>
+        <v>-887.3159781771235</v>
       </c>
       <c r="D86">
-        <v>277.7252065404918</v>
+        <v>274.9840218228765</v>
       </c>
       <c r="E86">
-        <v>-95.92000000000007</v>
+        <v>-77.29999999999995</v>
       </c>
       <c r="F86">
-        <v>1564.08</v>
+        <v>1582.7</v>
       </c>
       <c r="G86">
         <v>420.4</v>
@@ -8333,37 +8333,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M86">
-        <v>368.810064</v>
+        <v>373.20066</v>
       </c>
       <c r="N86">
-        <v>-319.710064</v>
+        <v>-324.1006600000001</v>
       </c>
       <c r="O86">
-        <v>-108.70142176</v>
+        <v>-110.1942244</v>
       </c>
       <c r="P86">
-        <v>-211.00864224</v>
+        <v>-213.9064356</v>
       </c>
       <c r="Q86">
-        <v>-19.10864223999997</v>
+        <v>-22.00643560000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2955847993948676</v>
+        <v>0.3122371193545255</v>
       </c>
       <c r="T86">
-        <v>3.255533290063318</v>
+        <v>3.472568842734207</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04526449148090492</v>
+        <v>0.04473196805171781</v>
       </c>
       <c r="W86">
-        <v>0.2251266329088026</v>
+        <v>0.2252522019334049</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1331308572967792</v>
+        <v>0.131564611916817</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.238299939546573</v>
+        <v>0.240199939546573</v>
       </c>
       <c r="C87">
-        <v>-887.3159781771235</v>
+        <v>-908.6235800492334</v>
       </c>
       <c r="D87">
-        <v>274.9840218228765</v>
+        <v>272.2964199507665</v>
       </c>
       <c r="E87">
-        <v>-77.29999999999995</v>
+        <v>-58.68000000000006</v>
       </c>
       <c r="F87">
-        <v>1582.7</v>
+        <v>1601.32</v>
       </c>
       <c r="G87">
         <v>420.4</v>
@@ -8415,37 +8415,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M87">
-        <v>373.20066</v>
+        <v>377.591256</v>
       </c>
       <c r="N87">
-        <v>-324.1006600000001</v>
+        <v>-328.491256</v>
       </c>
       <c r="O87">
-        <v>-110.1942244</v>
+        <v>-111.68702704</v>
       </c>
       <c r="P87">
-        <v>-213.9064356</v>
+        <v>-216.80422896</v>
       </c>
       <c r="Q87">
-        <v>-22.00643560000003</v>
+        <v>-24.90422895999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3122371193545255</v>
+        <v>0.3312683421655629</v>
       </c>
       <c r="T87">
-        <v>3.472568842734207</v>
+        <v>3.720609474358078</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04473196805171781</v>
+        <v>0.04421182888832573</v>
       </c>
       <c r="W87">
-        <v>0.2252522019334049</v>
+        <v>0.2253748507481328</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.131564611916817</v>
+        <v>0.1300347908480168</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.240199939546573</v>
+        <v>0.2420999395465731</v>
       </c>
       <c r="C88">
-        <v>-908.6235800492334</v>
+        <v>-929.8791549714751</v>
       </c>
       <c r="D88">
-        <v>272.2964199507665</v>
+        <v>269.6608450285249</v>
       </c>
       <c r="E88">
-        <v>-58.68000000000006</v>
+        <v>-40.05999999999995</v>
       </c>
       <c r="F88">
-        <v>1601.32</v>
+        <v>1619.94</v>
       </c>
       <c r="G88">
         <v>420.4</v>
@@ -8497,37 +8497,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M88">
-        <v>377.591256</v>
+        <v>381.981852</v>
       </c>
       <c r="N88">
-        <v>-328.491256</v>
+        <v>-332.881852</v>
       </c>
       <c r="O88">
-        <v>-111.68702704</v>
+        <v>-113.17982968</v>
       </c>
       <c r="P88">
-        <v>-216.80422896</v>
+        <v>-219.70202232</v>
       </c>
       <c r="Q88">
-        <v>-24.90422895999998</v>
+        <v>-27.80202231999996</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3312683421655629</v>
+        <v>0.3532274454090678</v>
       </c>
       <c r="T88">
-        <v>3.720609474358078</v>
+        <v>4.006810203154854</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04421182888832573</v>
+        <v>0.04370364694708062</v>
       </c>
       <c r="W88">
-        <v>0.2253748507481328</v>
+        <v>0.2254946800498784</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1300347908480168</v>
+        <v>0.1285401380796489</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2420999395465731</v>
+        <v>0.243999939546573</v>
       </c>
       <c r="C89">
-        <v>-929.8791549714751</v>
+        <v>-951.084199178483</v>
       </c>
       <c r="D89">
-        <v>269.6608450285249</v>
+        <v>267.075800821517</v>
       </c>
       <c r="E89">
-        <v>-40.05999999999995</v>
+        <v>-21.44000000000005</v>
       </c>
       <c r="F89">
-        <v>1619.94</v>
+        <v>1638.56</v>
       </c>
       <c r="G89">
         <v>420.4</v>
@@ -8579,37 +8579,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M89">
-        <v>381.981852</v>
+        <v>386.372448</v>
       </c>
       <c r="N89">
-        <v>-332.881852</v>
+        <v>-337.2724480000001</v>
       </c>
       <c r="O89">
-        <v>-113.17982968</v>
+        <v>-114.67263232</v>
       </c>
       <c r="P89">
-        <v>-219.70202232</v>
+        <v>-222.59981568</v>
       </c>
       <c r="Q89">
-        <v>-27.80202231999996</v>
+        <v>-30.69981568000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3532274454090678</v>
+        <v>0.3788463991931568</v>
       </c>
       <c r="T89">
-        <v>4.006810203154854</v>
+        <v>4.340711053417759</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04370364694708062</v>
+        <v>0.04320701459540924</v>
       </c>
       <c r="W89">
-        <v>0.2254946800498784</v>
+        <v>0.2256117859584025</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1285401380796489</v>
+        <v>0.12707945469238</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.243999939546573</v>
+        <v>0.245899939546573</v>
       </c>
       <c r="C90">
-        <v>-951.084199178483</v>
+        <v>-972.2401520763738</v>
       </c>
       <c r="D90">
-        <v>267.075800821517</v>
+        <v>264.5398479236263</v>
       </c>
       <c r="E90">
-        <v>-21.44000000000005</v>
+        <v>-2.819999999999936</v>
       </c>
       <c r="F90">
-        <v>1638.56</v>
+        <v>1657.18</v>
       </c>
       <c r="G90">
         <v>420.4</v>
@@ -8661,37 +8661,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M90">
-        <v>386.372448</v>
+        <v>390.763044</v>
       </c>
       <c r="N90">
-        <v>-337.2724480000001</v>
+        <v>-341.663044</v>
       </c>
       <c r="O90">
-        <v>-114.67263232</v>
+        <v>-116.16543496</v>
       </c>
       <c r="P90">
-        <v>-222.59981568</v>
+        <v>-225.49760904</v>
       </c>
       <c r="Q90">
-        <v>-30.69981568000003</v>
+        <v>-33.59760903999998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3788463991931568</v>
+        <v>0.4091233445743529</v>
       </c>
       <c r="T90">
-        <v>4.340711053417759</v>
+        <v>4.735321149183009</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04320701459540924</v>
+        <v>0.04272154252130352</v>
       </c>
       <c r="W90">
-        <v>0.2256117859584025</v>
+        <v>0.2257262602734766</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.12707945469238</v>
+        <v>0.1256515956508928</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.245899939546573</v>
+        <v>0.247799939546573</v>
       </c>
       <c r="C91">
-        <v>-972.2401520763738</v>
+        <v>-993.3483989153734</v>
       </c>
       <c r="D91">
-        <v>264.5398479236263</v>
+        <v>262.0516010846266</v>
       </c>
       <c r="E91">
-        <v>-2.819999999999936</v>
+        <v>15.79999999999995</v>
       </c>
       <c r="F91">
-        <v>1657.18</v>
+        <v>1675.8</v>
       </c>
       <c r="G91">
         <v>420.4</v>
@@ -8743,37 +8743,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M91">
-        <v>390.763044</v>
+        <v>395.15364</v>
       </c>
       <c r="N91">
-        <v>-341.663044</v>
+        <v>-346.05364</v>
       </c>
       <c r="O91">
-        <v>-116.16543496</v>
+        <v>-117.6582376</v>
       </c>
       <c r="P91">
-        <v>-225.49760904</v>
+        <v>-228.3954024</v>
       </c>
       <c r="Q91">
-        <v>-33.59760903999998</v>
+        <v>-36.49540239999996</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4091233445743529</v>
+        <v>0.4454556790317882</v>
       </c>
       <c r="T91">
-        <v>4.735321149183009</v>
+        <v>5.208853264101311</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04272154252130352</v>
+        <v>0.04224685871551126</v>
       </c>
       <c r="W91">
-        <v>0.2257262602734766</v>
+        <v>0.2258381907148825</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1256515956508928</v>
+        <v>0.1242554668103273</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.247799939546573</v>
+        <v>0.249699939546573</v>
       </c>
       <c r="C92">
-        <v>-993.3483989153734</v>
+        <v>-1014.410273313022</v>
       </c>
       <c r="D92">
-        <v>262.0516010846266</v>
+        <v>259.6097266869784</v>
       </c>
       <c r="E92">
-        <v>15.79999999999995</v>
+        <v>34.42000000000007</v>
       </c>
       <c r="F92">
-        <v>1675.8</v>
+        <v>1694.42</v>
       </c>
       <c r="G92">
         <v>420.4</v>
@@ -8825,37 +8825,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M92">
-        <v>395.15364</v>
+        <v>399.544236</v>
       </c>
       <c r="N92">
-        <v>-346.05364</v>
+        <v>-350.444236</v>
       </c>
       <c r="O92">
-        <v>-117.6582376</v>
+        <v>-119.15104024</v>
       </c>
       <c r="P92">
-        <v>-228.3954024</v>
+        <v>-231.29319576</v>
       </c>
       <c r="Q92">
-        <v>-36.49540239999996</v>
+        <v>-39.39319576</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4454556790317882</v>
+        <v>0.4898618655908759</v>
       </c>
       <c r="T92">
-        <v>5.208853264101311</v>
+        <v>5.787614737890347</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04224685871551126</v>
+        <v>0.04178260752083531</v>
       </c>
       <c r="W92">
-        <v>0.2258381907148825</v>
+        <v>0.225947661146587</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1242554668103273</v>
+        <v>0.1228900221201038</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.249699939546573</v>
+        <v>0.251599939546573</v>
       </c>
       <c r="C93">
-        <v>-1014.410273313022</v>
+        <v>-1035.427059637605</v>
       </c>
       <c r="D93">
-        <v>259.6097266869784</v>
+        <v>257.2129403623954</v>
       </c>
       <c r="E93">
-        <v>34.42000000000007</v>
+        <v>53.03999999999996</v>
       </c>
       <c r="F93">
-        <v>1694.42</v>
+        <v>1713.04</v>
       </c>
       <c r="G93">
         <v>420.4</v>
@@ -8907,37 +8907,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M93">
-        <v>399.544236</v>
+        <v>403.934832</v>
       </c>
       <c r="N93">
-        <v>-350.444236</v>
+        <v>-354.834832</v>
       </c>
       <c r="O93">
-        <v>-119.15104024</v>
+        <v>-120.64384288</v>
       </c>
       <c r="P93">
-        <v>-231.29319576</v>
+        <v>-234.19098912</v>
       </c>
       <c r="Q93">
-        <v>-39.39319576</v>
+        <v>-42.29098911999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4898618655908759</v>
+        <v>0.5453695987897355</v>
       </c>
       <c r="T93">
-        <v>5.787614737890347</v>
+        <v>6.511066580126641</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04178260752083531</v>
+        <v>0.04132844874343493</v>
       </c>
       <c r="W93">
-        <v>0.225947661146587</v>
+        <v>0.2260547517862981</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1228900221201038</v>
+        <v>0.1215542610101028</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.251599939546573</v>
+        <v>0.2534999395465731</v>
       </c>
       <c r="C94">
-        <v>-1035.427059637605</v>
+        <v>-1056.399995260771</v>
       </c>
       <c r="D94">
-        <v>257.2129403623954</v>
+        <v>254.8600047392292</v>
       </c>
       <c r="E94">
-        <v>53.03999999999996</v>
+        <v>71.66000000000008</v>
       </c>
       <c r="F94">
-        <v>1713.04</v>
+        <v>1731.66</v>
       </c>
       <c r="G94">
         <v>420.4</v>
@@ -8989,37 +8989,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M94">
-        <v>403.934832</v>
+        <v>408.325428</v>
       </c>
       <c r="N94">
-        <v>-354.834832</v>
+        <v>-359.2254280000001</v>
       </c>
       <c r="O94">
-        <v>-120.64384288</v>
+        <v>-122.13664552</v>
       </c>
       <c r="P94">
-        <v>-234.19098912</v>
+        <v>-237.08878248</v>
       </c>
       <c r="Q94">
-        <v>-42.29098911999998</v>
+        <v>-45.18878248000004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5453695987897355</v>
+        <v>0.6167366843311263</v>
       </c>
       <c r="T94">
-        <v>6.511066580126641</v>
+        <v>7.441218948716163</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04132844874343493</v>
+        <v>0.0408840568214625</v>
       </c>
       <c r="W94">
-        <v>0.2260547517862981</v>
+        <v>0.2261595394014992</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1215542610101028</v>
+        <v>0.1202472259454779</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2534999395465731</v>
+        <v>0.255399939546573</v>
       </c>
       <c r="C95">
-        <v>-1056.399995260771</v>
+        <v>-1077.330272687625</v>
       </c>
       <c r="D95">
-        <v>254.8600047392292</v>
+        <v>252.5497273123747</v>
       </c>
       <c r="E95">
-        <v>71.66000000000008</v>
+        <v>90.2800000000002</v>
       </c>
       <c r="F95">
-        <v>1731.66</v>
+        <v>1750.28</v>
       </c>
       <c r="G95">
         <v>420.4</v>
@@ -9071,37 +9071,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M95">
-        <v>408.325428</v>
+        <v>412.7160240000001</v>
       </c>
       <c r="N95">
-        <v>-359.2254280000001</v>
+        <v>-363.616024</v>
       </c>
       <c r="O95">
-        <v>-122.13664552</v>
+        <v>-123.62944816</v>
       </c>
       <c r="P95">
-        <v>-237.08878248</v>
+        <v>-239.98657584</v>
       </c>
       <c r="Q95">
-        <v>-45.18878248000004</v>
+        <v>-48.08657583999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6167366843311263</v>
+        <v>0.7118927983863144</v>
       </c>
       <c r="T95">
-        <v>7.441218948716163</v>
+        <v>8.681422106835527</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0408840568214625</v>
+        <v>0.0404491200467661</v>
       </c>
       <c r="W95">
-        <v>0.2261595394014992</v>
+        <v>0.2262620974929726</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1202472259454779</v>
+        <v>0.1189680001375474</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.255399939546573</v>
+        <v>0.257299939546573</v>
       </c>
       <c r="C96">
-        <v>-1077.330272687625</v>
+        <v>-1098.219041572015</v>
       </c>
       <c r="D96">
-        <v>252.5497273123747</v>
+        <v>250.2809584279853</v>
       </c>
       <c r="E96">
-        <v>90.2800000000002</v>
+        <v>108.9000000000001</v>
       </c>
       <c r="F96">
-        <v>1750.28</v>
+        <v>1768.9</v>
       </c>
       <c r="G96">
         <v>420.4</v>
@@ -9153,37 +9153,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M96">
-        <v>412.7160240000001</v>
+        <v>417.10662</v>
       </c>
       <c r="N96">
-        <v>-363.616024</v>
+        <v>-368.00662</v>
       </c>
       <c r="O96">
-        <v>-123.62944816</v>
+        <v>-125.1222508</v>
       </c>
       <c r="P96">
-        <v>-239.98657584</v>
+        <v>-242.8843692</v>
       </c>
       <c r="Q96">
-        <v>-48.08657583999999</v>
+        <v>-50.98436919999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7118927983863144</v>
+        <v>0.8451113580635775</v>
       </c>
       <c r="T96">
-        <v>8.681422106835527</v>
+        <v>10.41770652820264</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0404491200467661</v>
+        <v>0.04002333983574751</v>
       </c>
       <c r="W96">
-        <v>0.2262620974929726</v>
+        <v>0.2263624964667308</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1189680001375474</v>
+        <v>0.1177157053992575</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.257299939546573</v>
+        <v>0.2591999395465731</v>
       </c>
       <c r="C97">
-        <v>-1098.219041572015</v>
+        <v>-1119.06741062415</v>
       </c>
       <c r="D97">
-        <v>250.2809584279853</v>
+        <v>248.0525893758498</v>
       </c>
       <c r="E97">
-        <v>108.9000000000001</v>
+        <v>127.5200000000002</v>
       </c>
       <c r="F97">
-        <v>1768.9</v>
+        <v>1787.52</v>
       </c>
       <c r="G97">
         <v>420.4</v>
@@ -9235,37 +9235,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M97">
-        <v>417.10662</v>
+        <v>421.4972160000001</v>
       </c>
       <c r="N97">
-        <v>-368.00662</v>
+        <v>-372.3972160000001</v>
       </c>
       <c r="O97">
-        <v>-125.1222508</v>
+        <v>-126.61505344</v>
       </c>
       <c r="P97">
-        <v>-242.8843692</v>
+        <v>-245.78216256</v>
       </c>
       <c r="Q97">
-        <v>-50.98436919999997</v>
+        <v>-53.88216256000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8451113580635775</v>
+        <v>1.044939197579472</v>
       </c>
       <c r="T97">
-        <v>10.41770652820264</v>
+        <v>13.0221331602533</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04002333983574751</v>
+        <v>0.0396064300457918</v>
       </c>
       <c r="W97">
-        <v>0.2263624964667308</v>
+        <v>0.2264608037952023</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1177157053992575</v>
+        <v>0.1164895001346818</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2591999395465731</v>
+        <v>0.2610999395465731</v>
       </c>
       <c r="C98">
-        <v>-1119.06741062415</v>
+        <v>-1139.876449417225</v>
       </c>
       <c r="D98">
-        <v>248.0525893758498</v>
+        <v>245.863550582775</v>
       </c>
       <c r="E98">
-        <v>127.52</v>
+        <v>146.1399999999999</v>
       </c>
       <c r="F98">
-        <v>1787.52</v>
+        <v>1806.14</v>
       </c>
       <c r="G98">
         <v>420.4</v>
@@ -9317,37 +9317,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M98">
-        <v>421.497216</v>
+        <v>425.887812</v>
       </c>
       <c r="N98">
-        <v>-372.3972160000001</v>
+        <v>-376.787812</v>
       </c>
       <c r="O98">
-        <v>-126.61505344</v>
+        <v>-128.10785608</v>
       </c>
       <c r="P98">
-        <v>-245.78216256</v>
+        <v>-248.67995592</v>
       </c>
       <c r="Q98">
-        <v>-53.88216256000001</v>
+        <v>-56.77995591999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.04493919757947</v>
+        <v>1.377985596772626</v>
       </c>
       <c r="T98">
-        <v>13.02213316025327</v>
+        <v>17.36284421367102</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0396064300457918</v>
+        <v>0.03919811633397952</v>
       </c>
       <c r="W98">
-        <v>0.2264608037952023</v>
+        <v>0.2265570841684476</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1164895001346817</v>
+        <v>0.1152885774528809</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2610999395465731</v>
+        <v>0.262999939546573</v>
       </c>
       <c r="C99">
-        <v>-1139.876449417225</v>
+        <v>-1160.647190099209</v>
       </c>
       <c r="D99">
-        <v>245.863550582775</v>
+        <v>243.712809900791</v>
       </c>
       <c r="E99">
-        <v>146.1399999999999</v>
+        <v>164.76</v>
       </c>
       <c r="F99">
-        <v>1806.14</v>
+        <v>1824.76</v>
       </c>
       <c r="G99">
         <v>420.4</v>
@@ -9399,37 +9399,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M99">
-        <v>425.887812</v>
+        <v>430.278408</v>
       </c>
       <c r="N99">
-        <v>-376.787812</v>
+        <v>-381.178408</v>
       </c>
       <c r="O99">
-        <v>-128.10785608</v>
+        <v>-129.60065872</v>
       </c>
       <c r="P99">
-        <v>-248.67995592</v>
+        <v>-251.57774928</v>
       </c>
       <c r="Q99">
-        <v>-56.77995591999999</v>
+        <v>-59.67774927999997</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.377985596772626</v>
+        <v>2.044078395158939</v>
       </c>
       <c r="T99">
-        <v>17.36284421367102</v>
+        <v>26.04426632050653</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03919811633397952</v>
+        <v>0.03879813555506136</v>
       </c>
       <c r="W99">
-        <v>0.2265570841684476</v>
+        <v>0.2266513996361165</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1152885774528809</v>
+        <v>0.1141121633972394</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.262999939546573</v>
+        <v>0.264899939546573</v>
       </c>
       <c r="C100">
-        <v>-1160.647190099209</v>
+        <v>-1181.380629015576</v>
       </c>
       <c r="D100">
-        <v>243.712809900791</v>
+        <v>241.5993709844235</v>
       </c>
       <c r="E100">
-        <v>164.76</v>
+        <v>183.3799999999999</v>
       </c>
       <c r="F100">
-        <v>1824.76</v>
+        <v>1843.38</v>
       </c>
       <c r="G100">
         <v>420.4</v>
@@ -9481,37 +9481,37 @@
         <v>49.09999999999999</v>
       </c>
       <c r="M100">
-        <v>430.278408</v>
+        <v>434.669004</v>
       </c>
       <c r="N100">
-        <v>-381.178408</v>
+        <v>-385.5690039999999</v>
       </c>
       <c r="O100">
-        <v>-129.60065872</v>
+        <v>-131.09346136</v>
       </c>
       <c r="P100">
-        <v>-251.57774928</v>
+        <v>-254.47554264</v>
       </c>
       <c r="Q100">
-        <v>-59.67774927999997</v>
+        <v>-62.57554263999995</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.044078395158939</v>
+        <v>4.042356790317879</v>
       </c>
       <c r="T100">
-        <v>26.04426632050653</v>
+        <v>52.08853264101306</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03879813555506136</v>
+        <v>0.03840623519591933</v>
       </c>
       <c r="W100">
-        <v>0.2266513996361165</v>
+        <v>0.2267438097408022</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1141121633972394</v>
+        <v>0.1129595152821158</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.264899939546573</v>
-      </c>
-      <c r="C101">
-        <v>-1181.380629015576</v>
-      </c>
-      <c r="D101">
-        <v>241.5993709844235</v>
-      </c>
-      <c r="E101">
-        <v>183.3799999999999</v>
-      </c>
-      <c r="F101">
-        <v>1843.38</v>
-      </c>
-      <c r="G101">
-        <v>420.4</v>
-      </c>
-      <c r="H101">
-        <v>202</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>241</v>
-      </c>
-      <c r="K101">
-        <v>191.9</v>
-      </c>
-      <c r="L101">
-        <v>49.09999999999999</v>
-      </c>
-      <c r="M101">
-        <v>434.669004</v>
-      </c>
-      <c r="N101">
-        <v>-385.5690039999999</v>
-      </c>
-      <c r="O101">
-        <v>-131.09346136</v>
-      </c>
-      <c r="P101">
-        <v>-254.47554264</v>
-      </c>
-      <c r="Q101">
-        <v>-62.57554263999995</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.042356790317879</v>
-      </c>
-      <c r="T101">
-        <v>52.08853264101306</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03840623519591933</v>
-      </c>
-      <c r="W101">
-        <v>0.2267438097408022</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1129595152821158</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
